--- a/database/event/1986/event_1986_evp_summary.xlsx
+++ b/database/event/1986/event_1986_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.0213</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3054</v>
+        <v>2.2452</v>
       </c>
       <c r="E2" t="n">
         <v>6.7498</v>
@@ -548,7 +548,7 @@
         <v>3.9495</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2567</v>
+        <v>2.1972</v>
       </c>
       <c r="E3" t="n">
         <v>6.6292</v>
@@ -594,7 +594,7 @@
         <v>2.9099</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5517</v>
+        <v>1.502</v>
       </c>
       <c r="E4" t="n">
         <v>4.8842</v>
@@ -640,7 +640,7 @@
         <v>2.1561</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0406</v>
+        <v>0.9979</v>
       </c>
       <c r="E5" t="n">
         <v>3.619</v>
@@ -686,7 +686,7 @@
         <v>1.7031</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7335</v>
+        <v>0.695</v>
       </c>
       <c r="E6" t="n">
         <v>2.8587</v>
@@ -732,7 +732,7 @@
         <v>1.5025</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5974</v>
+        <v>0.5608</v>
       </c>
       <c r="E7" t="n">
         <v>2.5219</v>
@@ -778,7 +778,7 @@
         <v>1.4521</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5633</v>
+        <v>0.5272</v>
       </c>
       <c r="E8" t="n">
         <v>2.4374</v>
@@ -824,7 +824,7 @@
         <v>1.287</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4513</v>
+        <v>0.4167</v>
       </c>
       <c r="E9" t="n">
         <v>2.1602</v>
@@ -870,7 +870,7 @@
         <v>1.0059</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2607</v>
+        <v>0.2287</v>
       </c>
       <c r="E10" t="n">
         <v>1.6884</v>
@@ -916,7 +916,7 @@
         <v>0.8749</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1719</v>
+        <v>0.1411</v>
       </c>
       <c r="E11" t="n">
         <v>1.4685</v>
@@ -962,7 +962,7 @@
         <v>0.7338</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0762</v>
+        <v>0.0468</v>
       </c>
       <c r="E12" t="n">
         <v>1.2316</v>
@@ -1008,7 +1008,7 @@
         <v>0.7118</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0613</v>
+        <v>0.0321</v>
       </c>
       <c r="E13" t="n">
         <v>1.1948</v>
@@ -1054,7 +1054,7 @@
         <v>0.4928</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0872</v>
+        <v>-0.1144</v>
       </c>
       <c r="E14" t="n">
         <v>0.8270999999999999</v>
@@ -1100,7 +1100,7 @@
         <v>0.2816</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2304</v>
+        <v>-0.2556</v>
       </c>
       <c r="E15" t="n">
         <v>0.4726</v>
@@ -1146,7 +1146,7 @@
         <v>0.1829</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2973</v>
+        <v>-0.3216</v>
       </c>
       <c r="E16" t="n">
         <v>0.307</v>
@@ -1192,7 +1192,7 @@
         <v>0.1808</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2988</v>
+        <v>-0.323</v>
       </c>
       <c r="E17" t="n">
         <v>0.3034</v>
@@ -1238,7 +1238,7 @@
         <v>0.0922</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3588</v>
+        <v>-0.3822</v>
       </c>
       <c r="E18" t="n">
         <v>0.1548</v>
@@ -1284,7 +1284,7 @@
         <v>-0.0164</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4325</v>
+        <v>-0.4549</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0276</v>
@@ -1330,7 +1330,7 @@
         <v>-0.0375</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4468</v>
+        <v>-0.469</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0629</v>
@@ -1376,7 +1376,7 @@
         <v>-0.0604</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4623</v>
+        <v>-0.4843</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1013</v>
@@ -1422,7 +1422,7 @@
         <v>-0.1846</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5466</v>
+        <v>-0.5674</v>
       </c>
       <c r="E22" t="n">
         <v>-0.3099</v>
@@ -1468,7 +1468,7 @@
         <v>-0.2035</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5593</v>
+        <v>-0.58</v>
       </c>
       <c r="E23" t="n">
         <v>-0.3415</v>
@@ -1514,7 +1514,7 @@
         <v>-0.3228</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6402</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-0.5417999999999999</v>
@@ -1560,7 +1560,7 @@
         <v>-0.3759</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6763</v>
+        <v>-0.6953</v>
       </c>
       <c r="E25" t="n">
         <v>-0.631</v>
@@ -1606,7 +1606,7 @@
         <v>-0.4516</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7276</v>
+        <v>-0.7459</v>
       </c>
       <c r="E26" t="n">
         <v>-0.758</v>
@@ -1652,7 +1652,7 @@
         <v>-0.5289</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.78</v>
+        <v>-0.7976</v>
       </c>
       <c r="E27" t="n">
         <v>-0.8878</v>
@@ -1698,7 +1698,7 @@
         <v>-0.5800999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8147</v>
+        <v>-0.8318</v>
       </c>
       <c r="E28" t="n">
         <v>-0.9737</v>
@@ -1744,7 +1744,7 @@
         <v>-0.5807</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8151</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>-0.9747</v>
@@ -1790,7 +1790,7 @@
         <v>-0.7402</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9233</v>
+        <v>-0.9389</v>
       </c>
       <c r="E30" t="n">
         <v>-1.2425</v>
@@ -1836,7 +1836,7 @@
         <v>-0.8774999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.0164</v>
+        <v>-1.0307</v>
       </c>
       <c r="E31" t="n">
         <v>-1.4729</v>
@@ -1882,7 +1882,7 @@
         <v>-0.8875999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0232</v>
+        <v>-1.0374</v>
       </c>
       <c r="E32" t="n">
         <v>-1.4898</v>
@@ -1928,7 +1928,7 @@
         <v>-0.988</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0913</v>
+        <v>-1.1046</v>
       </c>
       <c r="E33" t="n">
         <v>-1.6583</v>
@@ -1974,7 +1974,7 @@
         <v>-1.0851</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1572</v>
+        <v>-1.1696</v>
       </c>
       <c r="E34" t="n">
         <v>-1.8214</v>
@@ -2020,7 +2020,7 @@
         <v>-1.0994</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1668</v>
+        <v>-1.1791</v>
       </c>
       <c r="E35" t="n">
         <v>-1.8453</v>
@@ -2066,7 +2066,7 @@
         <v>-1.1554</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2048</v>
+        <v>-1.2166</v>
       </c>
       <c r="E36" t="n">
         <v>-1.9394</v>
@@ -2112,7 +2112,7 @@
         <v>-1.1915</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E37" t="n">
         <v>-2</v>
@@ -2158,7 +2158,7 @@
         <v>-1.2331</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2575</v>
+        <v>-1.2685</v>
       </c>
       <c r="E38" t="n">
         <v>-2.0697</v>
@@ -2204,7 +2204,7 @@
         <v>-1.662</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5483</v>
+        <v>-1.5553</v>
       </c>
       <c r="E39" t="n">
         <v>-2.7896</v>
@@ -2250,7 +2250,7 @@
         <v>-1.7581</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6135</v>
+        <v>-1.6196</v>
       </c>
       <c r="E40" t="n">
         <v>-2.951</v>
@@ -2296,7 +2296,7 @@
         <v>-2.3905</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0423</v>
+        <v>-2.0425</v>
       </c>
       <c r="E41" t="n">
         <v>-4.0124</v>
@@ -2342,7 +2342,7 @@
         <v>-2.6565</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.2227</v>
+        <v>-2.2203</v>
       </c>
       <c r="E42" t="n">
         <v>-4.4589</v>

--- a/database/event/1986/event_1986_evp_summary.xlsx
+++ b/database/event/1986/event_1986_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7498</v>
+        <v>6.554</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0213</v>
+        <v>3.9047</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2452</v>
+        <v>2.3208</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7498</v>
+        <v>6.554</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8663</v>
+        <v>4.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8835</v>
+        <v>2.1022</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3138</v>
+        <v>13.0205</v>
       </c>
       <c r="I2" t="n">
-        <v>5.928</v>
+        <v>6.7701</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8835</v>
+        <v>2.1022</v>
       </c>
       <c r="K2" t="n">
         <v>189</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>7.8115</v>
+        <v>8.872299999999999</v>
       </c>
       <c r="N2" t="n">
         <v>388</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6292</v>
+        <v>5.8206</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9495</v>
+        <v>3.4677</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1972</v>
+        <v>1.9897</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6292</v>
+        <v>5.8206</v>
       </c>
       <c r="F3" t="n">
-        <v>4.221</v>
+        <v>3.7065</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4082</v>
+        <v>2.1141</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4216</v>
+        <v>7.5732</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5838</v>
+        <v>3.9377</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4082</v>
+        <v>2.1141</v>
       </c>
       <c r="K3" t="n">
         <v>149</v>
@@ -575,7 +575,7 @@
         <v>192</v>
       </c>
       <c r="M3" t="n">
-        <v>5.992</v>
+        <v>6.0518</v>
       </c>
       <c r="N3" t="n">
         <v>341</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8842</v>
+        <v>4.4119</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9099</v>
+        <v>2.6285</v>
       </c>
       <c r="D4" t="n">
-        <v>1.502</v>
+        <v>1.3537</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8842</v>
+        <v>4.4119</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8447</v>
+        <v>3.4093</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0395</v>
+        <v>1.0026</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8447</v>
+        <v>6.526</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1162</v>
+        <v>3.3932</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0395</v>
+        <v>1.0026</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
@@ -621,7 +621,7 @@
         <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1557</v>
+        <v>4.3958</v>
       </c>
       <c r="N4" t="n">
         <v>165</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.619</v>
+        <v>3.4737</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1561</v>
+        <v>2.0695</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9979</v>
+        <v>0.9302</v>
       </c>
       <c r="E5" t="n">
-        <v>3.619</v>
+        <v>3.4737</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5579</v>
+        <v>3.2245</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0611</v>
+        <v>0.2492</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5579</v>
+        <v>5.8747</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8838</v>
+        <v>3.0546</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0611</v>
+        <v>0.2492</v>
       </c>
       <c r="K5" t="n">
         <v>189</v>
@@ -667,7 +667,7 @@
         <v>199</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9449</v>
+        <v>3.3038</v>
       </c>
       <c r="N5" t="n">
         <v>388</v>
@@ -676,277 +676,277 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8587</v>
+        <v>2.956</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7031</v>
+        <v>1.7611</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>0.6965</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8587</v>
+        <v>2.956</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8568</v>
+        <v>2.956</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9981</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8568</v>
+        <v>3.1311</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1261</v>
+        <v>3.1311</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9981</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="L6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.128</v>
+        <v>3.1311</v>
       </c>
       <c r="N6" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5219</v>
+        <v>2.6581</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5025</v>
+        <v>1.5836</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5608</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5219</v>
+        <v>2.6581</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5219</v>
+        <v>1.7336</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.9245</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5219</v>
+        <v>1.7336</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5219</v>
+        <v>0.9014</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.9245</v>
       </c>
       <c r="K7" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5219</v>
+        <v>1.8259</v>
       </c>
       <c r="N7" t="n">
-        <v>184</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4374</v>
+        <v>2.5164</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4521</v>
+        <v>1.4992</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5272</v>
+        <v>0.498</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4374</v>
+        <v>2.5164</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4374</v>
+        <v>3.1615</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.6451</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4374</v>
+        <v>5.653</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4374</v>
+        <v>2.9393</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.6451</v>
       </c>
       <c r="K8" t="n">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4374</v>
+        <v>2.2942</v>
       </c>
       <c r="N8" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1602</v>
+        <v>2.5077</v>
       </c>
       <c r="C9" t="n">
-        <v>1.287</v>
+        <v>1.494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4167</v>
+        <v>0.4941</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1602</v>
+        <v>2.5077</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4393</v>
+        <v>2.5077</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2791</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4393</v>
+        <v>2.5077</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9771</v>
+        <v>2.5077</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2791</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="L9" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.698</v>
+        <v>2.5077</v>
       </c>
       <c r="N9" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6884</v>
+        <v>2.413</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0059</v>
+        <v>1.4376</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2287</v>
+        <v>0.4513</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6884</v>
+        <v>2.413</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6786</v>
+        <v>2.6154</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0098</v>
+        <v>-0.2024</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6786</v>
+        <v>3.7288</v>
       </c>
       <c r="I10" t="n">
-        <v>0.55</v>
+        <v>1.9388</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0098</v>
+        <v>-0.2024</v>
       </c>
       <c r="K10" t="n">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5598</v>
+        <v>1.7364</v>
       </c>
       <c r="N10" t="n">
-        <v>388</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.4685</v>
+        <v>2.257</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8749</v>
+        <v>1.3447</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1411</v>
+        <v>0.3809</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4685</v>
+        <v>2.257</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0403</v>
+        <v>2.257</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4282</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0403</v>
+        <v>2.257</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8431999999999999</v>
+        <v>2.257</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4282</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2714</v>
+        <v>2.257</v>
       </c>
       <c r="N11" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2316</v>
+        <v>2.1638</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7338</v>
+        <v>1.2891</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0468</v>
+        <v>0.3388</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2316</v>
+        <v>2.1638</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6019</v>
+        <v>2.297</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3703</v>
+        <v>-0.1332</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6019</v>
+        <v>2.607</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2984</v>
+        <v>1.3555</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3703</v>
+        <v>-0.1332</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9280999999999999</v>
+        <v>1.2223</v>
       </c>
       <c r="N12" t="n">
         <v>165</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1948</v>
+        <v>2.0676</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7118</v>
+        <v>1.2318</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0321</v>
+        <v>0.2954</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1948</v>
+        <v>2.0676</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9394</v>
+        <v>1.6501</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7446</v>
+        <v>0.4175</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9394</v>
+        <v>1.6501</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3825</v>
+        <v>0.858</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7446</v>
+        <v>0.4175</v>
       </c>
       <c r="K13" t="n">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6378999999999999</v>
+        <v>1.2755</v>
       </c>
       <c r="N13" t="n">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.1046</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4928</v>
+        <v>0.6581</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1144</v>
+        <v>-0.1393</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.1046</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8270999999999999</v>
+        <v>2.779</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1.6744</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8270999999999999</v>
+        <v>4.305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8270999999999999</v>
+        <v>2.2384</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-1.6744</v>
       </c>
       <c r="K14" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.5639999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>178</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4726</v>
+        <v>0.7529</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2816</v>
+        <v>0.4486</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2556</v>
+        <v>-0.2981</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4726</v>
+        <v>0.7529</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4726</v>
+        <v>0.7529</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4726</v>
+        <v>0.7529</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4726</v>
+        <v>0.7529</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4726</v>
+        <v>0.7529</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.307</v>
+        <v>0.5997</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1829</v>
+        <v>0.3573</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3216</v>
+        <v>-0.3673</v>
       </c>
       <c r="E16" t="n">
-        <v>0.307</v>
+        <v>0.5997</v>
       </c>
       <c r="F16" t="n">
-        <v>0.307</v>
+        <v>0.5997</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.307</v>
+        <v>0.5997</v>
       </c>
       <c r="I16" t="n">
-        <v>0.307</v>
+        <v>0.5997</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.307</v>
+        <v>0.5997</v>
       </c>
       <c r="N16" t="n">
         <v>102</v>
@@ -1182,369 +1182,369 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mOE</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3034</v>
+        <v>0.5569</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1808</v>
+        <v>0.3318</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.323</v>
+        <v>-0.3866</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3034</v>
+        <v>0.5569</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3034</v>
+        <v>0.3135</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2434</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3034</v>
+        <v>0.3135</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3034</v>
+        <v>0.163</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2434</v>
       </c>
       <c r="K17" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3034</v>
+        <v>0.4064</v>
       </c>
       <c r="N17" t="n">
-        <v>51</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1548</v>
+        <v>0.3532</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0922</v>
+        <v>0.2104</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3822</v>
+        <v>-0.4786</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1548</v>
+        <v>0.3532</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0109</v>
+        <v>0.3532</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1439</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0109</v>
+        <v>0.3532</v>
       </c>
       <c r="I18" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.3532</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1439</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1527</v>
+        <v>0.3532</v>
       </c>
       <c r="N18" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0276</v>
+        <v>0.297</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0164</v>
+        <v>0.1769</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4549</v>
+        <v>-0.5039</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0276</v>
+        <v>0.297</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0276</v>
+        <v>0.9043</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6073</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0276</v>
+        <v>0.9043</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0276</v>
+        <v>0.4702</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6073</v>
       </c>
       <c r="K19" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0276</v>
+        <v>-0.1370999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>mOE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0629</v>
+        <v>0.2841</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0375</v>
+        <v>0.1693</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.469</v>
+        <v>-0.5098</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0629</v>
+        <v>0.2841</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0629</v>
+        <v>0.2841</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0629</v>
+        <v>0.2841</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0629</v>
+        <v>0.2841</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>184</v>
+        <v>51</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0629</v>
+        <v>0.2841</v>
       </c>
       <c r="N20" t="n">
-        <v>184</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1013</v>
+        <v>0.2117</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0604</v>
+        <v>0.1261</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4843</v>
+        <v>-0.5424</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1013</v>
+        <v>0.2117</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1013</v>
+        <v>0.2117</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1013</v>
+        <v>0.2117</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1013</v>
+        <v>0.2117</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1013</v>
+        <v>0.2117</v>
       </c>
       <c r="N21" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3099</v>
+        <v>0.1686</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1846</v>
+        <v>0.1004</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5674</v>
+        <v>-0.5619</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3099</v>
+        <v>0.1686</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3099</v>
+        <v>0.6506</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3099</v>
+        <v>0.6506</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3099</v>
+        <v>0.3383</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.482</v>
       </c>
       <c r="K22" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3099</v>
+        <v>-0.1437</v>
       </c>
       <c r="N22" t="n">
-        <v>127</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3415</v>
+        <v>-0.0743</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2035</v>
+        <v>-0.0443</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.58</v>
+        <v>-0.6716</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3415</v>
+        <v>-0.0743</v>
       </c>
       <c r="F23" t="n">
-        <v>0.587</v>
+        <v>-0.0743</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9285</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.587</v>
+        <v>-0.0743</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4758</v>
+        <v>-0.0743</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9285</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="L23" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4527</v>
+        <v>-0.0743</v>
       </c>
       <c r="N23" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.1169</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.3228</v>
+        <v>-0.0696</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6908</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.1169</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1695</v>
+        <v>-0.1169</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7113</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1695</v>
+        <v>-0.1169</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1374</v>
+        <v>-0.1169</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7113</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="L24" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5739000000000001</v>
+        <v>-0.1169</v>
       </c>
       <c r="N24" t="n">
-        <v>341</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.631</v>
+        <v>-0.3738</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.3759</v>
+        <v>-0.2227</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6953</v>
+        <v>-0.8068</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.631</v>
+        <v>-0.3738</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1048</v>
+        <v>-0.8307</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4738</v>
+        <v>0.4569</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1048</v>
+        <v>-0.8307</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8955</v>
+        <v>-0.4319</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4738</v>
+        <v>0.4569</v>
       </c>
       <c r="K25" t="n">
         <v>149</v>
@@ -1587,7 +1587,7 @@
         <v>192</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4217</v>
+        <v>0.02499999999999997</v>
       </c>
       <c r="N25" t="n">
         <v>341</v>
@@ -1596,185 +1596,185 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.758</v>
+        <v>-0.5011</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.4516</v>
+        <v>-0.2985</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7459</v>
+        <v>-0.8642</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.758</v>
+        <v>-0.5011</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.758</v>
+        <v>-0.3358</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.1653</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.758</v>
+        <v>-0.3358</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.758</v>
+        <v>-0.1746</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.1653</v>
       </c>
       <c r="K26" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.758</v>
+        <v>-0.3399</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8878</v>
+        <v>-0.5329</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.5289</v>
+        <v>-0.3175</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7976</v>
+        <v>-0.8786</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8878</v>
+        <v>-0.5329</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8878</v>
+        <v>-0.5329</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8878</v>
+        <v>-0.5329</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8878</v>
+        <v>-0.5329</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8878</v>
+        <v>-0.5329</v>
       </c>
       <c r="N27" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.9737</v>
+        <v>-0.5491</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3271</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8318</v>
+        <v>-0.8859</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.9737</v>
+        <v>-0.5491</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6338</v>
+        <v>-0.5491</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3399</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6338</v>
+        <v>-0.5491</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5137</v>
+        <v>-0.5491</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3399</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.8536</v>
+        <v>-0.5491</v>
       </c>
       <c r="N28" t="n">
-        <v>341</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9747</v>
+        <v>-0.6363</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.5807</v>
+        <v>-0.3791</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.9253</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9747</v>
+        <v>-0.6363</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9747</v>
+        <v>-0.6363</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9747</v>
+        <v>-0.6363</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9747</v>
+        <v>-0.6363</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9747</v>
+        <v>-0.6363</v>
       </c>
       <c r="N29" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.2425</v>
+        <v>-0.9563</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.7402</v>
+        <v>-0.5697</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.9389</v>
+        <v>-1.0697</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.2425</v>
+        <v>-0.9563</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.2425</v>
+        <v>-0.9563</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.2425</v>
+        <v>-0.9563</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.2425</v>
+        <v>-0.9563</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.2425</v>
+        <v>-0.9563</v>
       </c>
       <c r="N30" t="n">
         <v>184</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.4729</v>
+        <v>-1.0242</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.6102</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.0307</v>
+        <v>-1.1004</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.4729</v>
+        <v>-1.0242</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.4729</v>
+        <v>-1.0242</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.4729</v>
+        <v>-1.0242</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.4729</v>
+        <v>-1.0242</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.4729</v>
+        <v>-1.0242</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1872,170 +1872,170 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.4898</v>
+        <v>-1.1082</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.6602</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0374</v>
+        <v>-1.1383</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.4898</v>
+        <v>-1.1082</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.4898</v>
+        <v>-1.1082</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.4898</v>
+        <v>-1.1082</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.4898</v>
+        <v>-1.1082</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.4898</v>
+        <v>-1.1082</v>
       </c>
       <c r="N32" t="n">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.6583</v>
+        <v>-1.2099</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.988</v>
+        <v>-0.7208</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.1046</v>
+        <v>-1.1842</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.6583</v>
+        <v>-1.2099</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2309</v>
+        <v>-1.2099</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4274</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.2309</v>
+        <v>-1.2099</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9977</v>
+        <v>-1.2099</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4274</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="L33" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.4251</v>
+        <v>-1.2099</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.8214</v>
+        <v>-1.2973</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.0851</v>
+        <v>-0.7729</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1696</v>
+        <v>-1.2237</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.8214</v>
+        <v>-1.2973</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.8214</v>
+        <v>-1.2973</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.8214</v>
+        <v>-1.2973</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.8214</v>
+        <v>-1.2973</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.8214</v>
+        <v>-1.2973</v>
       </c>
       <c r="N34" t="n">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.8453</v>
+        <v>-1.3668</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.0994</v>
+        <v>-0.8143</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1791</v>
+        <v>-1.2551</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.8453</v>
+        <v>-1.3668</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.8453</v>
+        <v>-1.3668</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.8453</v>
+        <v>-1.3668</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.8453</v>
+        <v>-1.3668</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.8453</v>
+        <v>-1.3668</v>
       </c>
       <c r="N35" t="n">
         <v>178</v>
@@ -2056,277 +2056,277 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.9394</v>
+        <v>-1.623</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.1554</v>
+        <v>-0.9669</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2166</v>
+        <v>-1.3707</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.9394</v>
+        <v>-1.623</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.9394</v>
+        <v>-1.623</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.9394</v>
+        <v>-1.623</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.9394</v>
+        <v>-1.623</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.9394</v>
+        <v>-1.623</v>
       </c>
       <c r="N36" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2</v>
+        <v>-2.0888</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.1915</v>
+        <v>-1.2444</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2407</v>
+        <v>-1.581</v>
       </c>
       <c r="E37" t="n">
-        <v>-2</v>
+        <v>-2.0888</v>
       </c>
       <c r="F37" t="n">
-        <v>-2</v>
+        <v>-1.7909</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.2979</v>
       </c>
       <c r="H37" t="n">
-        <v>-2</v>
+        <v>-1.7909</v>
       </c>
       <c r="I37" t="n">
-        <v>-2</v>
+        <v>-0.9312</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.2979</v>
       </c>
       <c r="K37" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M37" t="n">
-        <v>-2</v>
+        <v>-1.2291</v>
       </c>
       <c r="N37" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.0697</v>
+        <v>-2.1045</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.2331</v>
+        <v>-1.2538</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2685</v>
+        <v>-1.5881</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.0697</v>
+        <v>-2.1045</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5067</v>
+        <v>-1.5684</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5361</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5067</v>
+        <v>-1.5684</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2212</v>
+        <v>-0.8155</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.5361</v>
       </c>
       <c r="K38" t="n">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="L38" t="n">
-        <v>58</v>
+        <v>199</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7842</v>
+        <v>-1.3516</v>
       </c>
       <c r="N38" t="n">
-        <v>165</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.7896</v>
+        <v>-2.4296</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.662</v>
+        <v>-1.4475</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.5553</v>
+        <v>-1.7349</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.7896</v>
+        <v>-2.4296</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6679</v>
+        <v>-2.0823</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1217</v>
+        <v>-0.3473</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6679</v>
+        <v>-2.0823</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3519</v>
+        <v>-1.0827</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.1217</v>
+        <v>-0.3473</v>
       </c>
       <c r="K39" t="n">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="L39" t="n">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.4736</v>
+        <v>-1.43</v>
       </c>
       <c r="N39" t="n">
-        <v>388</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.951</v>
+        <v>-3.9755</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.7581</v>
+        <v>-2.3685</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6196</v>
+        <v>-2.4328</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.951</v>
+        <v>-3.9755</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.7687</v>
+        <v>-3.9755</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1823</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.7687</v>
+        <v>-3.9755</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.2441</v>
+        <v>-3.9755</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1823</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="L40" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.4264</v>
+        <v>-3.9755</v>
       </c>
       <c r="N40" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.0124</v>
+        <v>-4.0048</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.3905</v>
+        <v>-2.3859</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0425</v>
+        <v>-2.446</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.0124</v>
+        <v>-4.0048</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.0124</v>
+        <v>-4.0302</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.0254</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.0124</v>
+        <v>-4.0302</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.0124</v>
+        <v>-2.0955</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.0254</v>
       </c>
       <c r="K41" t="n">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.0124</v>
+        <v>-2.0701</v>
       </c>
       <c r="N41" t="n">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42">
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-4.4589</v>
+        <v>-4.7916</v>
       </c>
       <c r="C42" t="n">
-        <v>-2.6565</v>
+        <v>-2.8547</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.2203</v>
+        <v>-2.8012</v>
       </c>
       <c r="E42" t="n">
-        <v>-4.4589</v>
+        <v>-4.7916</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.1962</v>
+        <v>-3.9661</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.2627</v>
+        <v>-0.8255</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.1962</v>
+        <v>-3.9661</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.5906</v>
+        <v>-2.0622</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.2627</v>
+        <v>-0.8255</v>
       </c>
       <c r="K42" t="n">
         <v>189</v>
@@ -2369,7 +2369,7 @@
         <v>199</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.8533</v>
+        <v>-2.8877</v>
       </c>
       <c r="N42" t="n">
         <v>388</v>
@@ -2475,10 +2475,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9701</v>
+        <v>0.9427</v>
       </c>
       <c r="J2" t="n">
-        <v>29.103</v>
+        <v>28.281</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4233</v>
+        <v>0.3761</v>
       </c>
       <c r="J3" t="n">
-        <v>12.699</v>
+        <v>11.283</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.252</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.252</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1666</v>
+        <v>-1.1638</v>
       </c>
       <c r="J6" t="n">
-        <v>-34.998</v>
+        <v>-34.914</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7538</v>
+        <v>0.9382</v>
       </c>
       <c r="J7" t="n">
-        <v>22.614</v>
+        <v>28.146</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2591</v>
+        <v>0.2772</v>
       </c>
       <c r="J8" t="n">
-        <v>7.773</v>
+        <v>8.316000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2321</v>
+        <v>-0.141</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.963</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3138</v>
+        <v>-0.1939</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.414</v>
+        <v>-5.817</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.49</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7709</v>
+        <v>-0.5248</v>
       </c>
       <c r="J11" t="n">
-        <v>-23.127</v>
+        <v>-15.744</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0894</v>
+        <v>1.0441</v>
       </c>
       <c r="J12" t="n">
-        <v>32.682</v>
+        <v>31.323</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3451</v>
+        <v>0.2949</v>
       </c>
       <c r="J13" t="n">
-        <v>10.353</v>
+        <v>8.847</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.103</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.09</v>
+        <v>-2.724</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.358</v>
+        <v>-0.3158</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.74</v>
+        <v>-9.474</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.58</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1623</v>
+        <v>-1.1591</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.869</v>
+        <v>-34.773</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3272</v>
+        <v>0.3607</v>
       </c>
       <c r="J17" t="n">
-        <v>9.816000000000001</v>
+        <v>10.821</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0047</v>
+        <v>-0.0166</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.141</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.131</v>
+        <v>-0.0835</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.93</v>
+        <v>-2.505</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1723</v>
+        <v>-0.1065</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.169</v>
+        <v>-3.195</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4426</v>
+        <v>-0.2824</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.278</v>
+        <v>-8.472</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.11</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3206</v>
+        <v>0.2615</v>
       </c>
       <c r="J22" t="n">
-        <v>7.0532</v>
+        <v>5.753</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0336</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7392</v>
+        <v>-0.1848</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2641</v>
+        <v>-0.1969</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.8102</v>
+        <v>-4.3318</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.67</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5139</v>
+        <v>-0.3395</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.3058</v>
+        <v>-7.469</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.44</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8076</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.7672</v>
+        <v>-12.1638</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5849</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>12.8678</v>
+        <v>11.2992</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.24</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3717</v>
+        <v>0.3293</v>
       </c>
       <c r="J28" t="n">
-        <v>8.1774</v>
+        <v>7.2446</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2512</v>
+        <v>0.2457</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5264</v>
+        <v>5.4054</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1535</v>
+        <v>0.1666</v>
       </c>
       <c r="J30" t="n">
-        <v>3.377</v>
+        <v>3.6652</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>1.06</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0674</v>
+        <v>0.0931</v>
       </c>
       <c r="J31" t="n">
-        <v>1.4828</v>
+        <v>2.0482</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2046</v>
+        <v>0.1561</v>
       </c>
       <c r="J32" t="n">
-        <v>6.138</v>
+        <v>4.683</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>0.97</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0419</v>
+        <v>-0.0436</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.257</v>
+        <v>-1.308</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1295</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.885</v>
+        <v>-2.799</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1974</v>
+        <v>-0.1262</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.922</v>
+        <v>-3.786</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4361</v>
+        <v>-0.2791</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.083</v>
+        <v>-8.372999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.31</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5272</v>
+        <v>0.4469</v>
       </c>
       <c r="J37" t="n">
-        <v>15.816</v>
+        <v>13.407</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3179</v>
+        <v>0.2556</v>
       </c>
       <c r="J38" t="n">
-        <v>9.537000000000001</v>
+        <v>7.668</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2868</v>
+        <v>0.2285</v>
       </c>
       <c r="J39" t="n">
-        <v>8.603999999999999</v>
+        <v>6.855</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4707</v>
+        <v>-0.3</v>
       </c>
       <c r="J40" t="n">
-        <v>-14.121</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4707</v>
+        <v>-0.3</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.121</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.51</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2139</v>
+        <v>1.1408</v>
       </c>
       <c r="J42" t="n">
-        <v>26.7058</v>
+        <v>25.0976</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.36</v>
       </c>
       <c r="I43" t="n">
-        <v>0.897</v>
+        <v>0.9127</v>
       </c>
       <c r="J43" t="n">
-        <v>19.734</v>
+        <v>20.0794</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.35</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8743</v>
+        <v>0.891</v>
       </c>
       <c r="J44" t="n">
-        <v>19.2346</v>
+        <v>19.602</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3202</v>
+        <v>0.3982</v>
       </c>
       <c r="J45" t="n">
-        <v>7.0444</v>
+        <v>8.760400000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.93</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4074</v>
+        <v>-0.3281</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.9628</v>
+        <v>-7.2182</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3221</v>
+        <v>0.3529</v>
       </c>
       <c r="J47" t="n">
-        <v>7.0862</v>
+        <v>7.7638</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.59</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5708</v>
+        <v>-0.3908</v>
       </c>
       <c r="J48" t="n">
-        <v>-12.5576</v>
+        <v>-8.5976</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.615</v>
+        <v>-0.4187</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.53</v>
+        <v>-9.211399999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.53</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6574</v>
+        <v>-0.4468</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.4628</v>
+        <v>-9.829599999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.52</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6712</v>
+        <v>-0.4562</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.7664</v>
+        <v>-10.0364</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3592</v>
+        <v>0.3692</v>
       </c>
       <c r="J52" t="n">
-        <v>8.98</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0196</v>
+        <v>-0.042</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.49</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1514</v>
+        <v>-0.1269</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.785</v>
+        <v>-3.1725</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.57</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6525</v>
+        <v>-0.4363</v>
       </c>
       <c r="J55" t="n">
-        <v>-16.3125</v>
+        <v>-10.9075</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6525</v>
+        <v>-0.4363</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.3125</v>
+        <v>-10.9075</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1398</v>
+        <v>0.8124</v>
       </c>
       <c r="J57" t="n">
-        <v>28.495</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.31</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8367</v>
+        <v>0.6251</v>
       </c>
       <c r="J58" t="n">
-        <v>20.9175</v>
+        <v>15.6275</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4423</v>
       </c>
       <c r="J59" t="n">
-        <v>12.715</v>
+        <v>11.0575</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2822</v>
+        <v>-0.2073</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.055</v>
+        <v>-5.1825</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.91</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4362</v>
+        <v>-0.3645</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.905</v>
+        <v>-9.112500000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.12</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2822</v>
+        <v>0.3031</v>
       </c>
       <c r="J62" t="n">
-        <v>11.288</v>
+        <v>12.124</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0483</v>
       </c>
       <c r="J63" t="n">
-        <v>2.76</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2595</v>
+        <v>-0.1604</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.38</v>
+        <v>-6.416</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.276</v>
+        <v>-0.171</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.04</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.276</v>
+        <v>-0.171</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.04</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3663</v>
+        <v>0.3186</v>
       </c>
       <c r="J67" t="n">
-        <v>14.652</v>
+        <v>12.744</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2702</v>
+        <v>0.229</v>
       </c>
       <c r="J68" t="n">
-        <v>10.808</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.03</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1605</v>
+        <v>0.13</v>
       </c>
       <c r="J69" t="n">
-        <v>6.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1605</v>
+        <v>-0.13</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.42</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5377</v>
+        <v>-0.4884</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.508</v>
+        <v>-19.536</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.15</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3412</v>
+        <v>0.3581</v>
       </c>
       <c r="J72" t="n">
-        <v>9.553599999999999</v>
+        <v>10.0268</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3258</v>
+        <v>0.3458</v>
       </c>
       <c r="J73" t="n">
-        <v>9.122400000000001</v>
+        <v>9.682399999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.86</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2637</v>
+        <v>-0.1673</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.3836</v>
+        <v>-4.6844</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.73</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4611</v>
+        <v>-0.297</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.9108</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5289</v>
+        <v>-0.3447</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.8092</v>
+        <v>-9.6516</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0176</v>
+        <v>0.7245</v>
       </c>
       <c r="J77" t="n">
-        <v>28.4928</v>
+        <v>20.286</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0727</v>
+        <v>0.0538</v>
       </c>
       <c r="J78" t="n">
-        <v>2.0356</v>
+        <v>1.5064</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2688</v>
+        <v>-0.2285</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.5264</v>
+        <v>-6.398</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.92</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3341</v>
+        <v>-0.2896</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.354799999999999</v>
+        <v>-8.1088</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7406</v>
+        <v>-0.6978</v>
       </c>
       <c r="J81" t="n">
-        <v>-20.7368</v>
+        <v>-19.5384</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6983</v>
+        <v>0.6445</v>
       </c>
       <c r="J82" t="n">
-        <v>20.949</v>
+        <v>19.335</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.18</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3466</v>
+        <v>0.3701</v>
       </c>
       <c r="J83" t="n">
-        <v>10.398</v>
+        <v>11.103</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1819</v>
+        <v>-0.1024</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.457</v>
+        <v>-3.072</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2993</v>
+        <v>-0.18</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.978999999999999</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.537</v>
+        <v>-0.3481</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.11</v>
+        <v>-10.443</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.15</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5833</v>
+        <v>0.4447</v>
       </c>
       <c r="J87" t="n">
-        <v>17.499</v>
+        <v>13.341</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.216</v>
+        <v>0.1532</v>
       </c>
       <c r="J88" t="n">
-        <v>6.48</v>
+        <v>4.596</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4105</v>
+        <v>-0.3848</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.315</v>
+        <v>-11.544</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5816</v>
+        <v>-0.5464</v>
       </c>
       <c r="J90" t="n">
-        <v>-17.448</v>
+        <v>-16.392</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.76</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.736</v>
+        <v>-0.7013</v>
       </c>
       <c r="J91" t="n">
-        <v>-22.08</v>
+        <v>-21.039</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.75</v>
       </c>
       <c r="I92" t="n">
-        <v>1.7261</v>
+        <v>1.4769</v>
       </c>
       <c r="J92" t="n">
-        <v>46.6047</v>
+        <v>39.8763</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.15</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4423</v>
+        <v>0.4477</v>
       </c>
       <c r="J93" t="n">
-        <v>11.9421</v>
+        <v>12.0879</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2426</v>
+        <v>0.2887</v>
       </c>
       <c r="J94" t="n">
-        <v>6.5502</v>
+        <v>7.7949</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.4441</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.7862</v>
+        <v>-11.9907</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6333</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.603</v>
+        <v>-17.0991</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.15</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3713</v>
+        <v>0.41</v>
       </c>
       <c r="J97" t="n">
-        <v>10.0251</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.063</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.701</v>
+        <v>-1.8765</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.89</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1554</v>
+        <v>-0.128</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.1958</v>
+        <v>-3.456</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.66</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5365</v>
+        <v>-0.3532</v>
       </c>
       <c r="J100" t="n">
-        <v>-14.4855</v>
+        <v>-9.5364</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.53</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.4743</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.0107</v>
+        <v>-12.8061</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.4633</v>
       </c>
       <c r="J102" t="n">
-        <v>14.2688</v>
+        <v>12.9724</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3579</v>
+        <v>0.3143</v>
       </c>
       <c r="J103" t="n">
-        <v>10.0212</v>
+        <v>8.8004</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.06</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1405</v>
+        <v>0.1191</v>
       </c>
       <c r="J104" t="n">
-        <v>3.934</v>
+        <v>3.3348</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3764</v>
+        <v>-0.2326</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.5392</v>
+        <v>-6.5128</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.8</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3907</v>
+        <v>-0.2427</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.9396</v>
+        <v>-6.7956</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5619</v>
+        <v>0.478</v>
       </c>
       <c r="J107" t="n">
-        <v>15.7332</v>
+        <v>13.384</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.356</v>
+        <v>0.2834</v>
       </c>
       <c r="J108" t="n">
-        <v>9.968</v>
+        <v>7.9352</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3102</v>
+        <v>0.2419</v>
       </c>
       <c r="J109" t="n">
-        <v>8.685600000000001</v>
+        <v>6.7732</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.6</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.6388</v>
+        <v>-0.4243</v>
       </c>
       <c r="J110" t="n">
-        <v>-17.8864</v>
+        <v>-11.8804</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7113</v>
+        <v>-0.479</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.9164</v>
+        <v>-13.412</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.84</v>
       </c>
       <c r="I112" t="n">
-        <v>1.832</v>
+        <v>1.5491</v>
       </c>
       <c r="J112" t="n">
-        <v>40.304</v>
+        <v>34.0802</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6361</v>
+        <v>0.6696</v>
       </c>
       <c r="J113" t="n">
-        <v>13.9942</v>
+        <v>14.7312</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4877</v>
+        <v>0.5535</v>
       </c>
       <c r="J114" t="n">
-        <v>10.7294</v>
+        <v>12.177</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3277</v>
+        <v>0.4018</v>
       </c>
       <c r="J115" t="n">
-        <v>7.2094</v>
+        <v>8.839600000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7861</v>
+        <v>-0.7359</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.2942</v>
+        <v>-16.1898</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.41</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7368</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>16.2096</v>
+        <v>20.4578</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1534</v>
+        <v>-0.1327</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.3748</v>
+        <v>-2.9194</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4527</v>
+        <v>-0.3002</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.9594</v>
+        <v>-6.6044</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.64</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5524</v>
+        <v>-0.3664</v>
       </c>
       <c r="J120" t="n">
-        <v>-12.1528</v>
+        <v>-8.0608</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.33</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9337</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>-20.5414</v>
+        <v>-14.3374</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7438</v>
+        <v>0.7004</v>
       </c>
       <c r="J122" t="n">
-        <v>22.314</v>
+        <v>21.012</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5131</v>
+        <v>0.4628</v>
       </c>
       <c r="J123" t="n">
-        <v>15.393</v>
+        <v>13.884</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3691</v>
+        <v>0.3211</v>
       </c>
       <c r="J124" t="n">
-        <v>11.073</v>
+        <v>9.632999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7155</v>
+        <v>-0.6716</v>
       </c>
       <c r="J125" t="n">
-        <v>-21.465</v>
+        <v>-20.148</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8115</v>
+        <v>-0.7732</v>
       </c>
       <c r="J126" t="n">
-        <v>-24.345</v>
+        <v>-23.196</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.62</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9112</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
-        <v>27.336</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.14</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3073</v>
+        <v>0.3372</v>
       </c>
       <c r="J128" t="n">
-        <v>9.218999999999999</v>
+        <v>10.116</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4454</v>
+        <v>-0.2838</v>
       </c>
       <c r="J129" t="n">
-        <v>-13.362</v>
+        <v>-8.513999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4863</v>
+        <v>-0.3128</v>
       </c>
       <c r="J130" t="n">
-        <v>-14.589</v>
+        <v>-9.384</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6645</v>
+        <v>-0.4435</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.935</v>
+        <v>-13.305</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9499</v>
+        <v>0.9418</v>
       </c>
       <c r="J132" t="n">
-        <v>22.7976</v>
+        <v>22.6032</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7915</v>
+        <v>0.7821</v>
       </c>
       <c r="J133" t="n">
-        <v>18.996</v>
+        <v>18.7704</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7199</v>
+        <v>0.7114</v>
       </c>
       <c r="J134" t="n">
-        <v>17.2776</v>
+        <v>17.0736</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0062</v>
+        <v>0.0574</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.1488</v>
+        <v>1.3776</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.87</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5448</v>
+        <v>-0.4783</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.0752</v>
+        <v>-11.4792</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4946</v>
+        <v>0.5788</v>
       </c>
       <c r="J137" t="n">
-        <v>11.8704</v>
+        <v>13.8912</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1818</v>
+        <v>-0.1472</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.3632</v>
+        <v>-3.5328</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2172</v>
+        <v>-0.1682</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.2128</v>
+        <v>-4.0368</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.62</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5854</v>
+        <v>-0.3883</v>
       </c>
       <c r="J140" t="n">
-        <v>-14.0496</v>
+        <v>-9.3192</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.51</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.4903</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.4072</v>
+        <v>-11.7672</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.08</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2513</v>
+        <v>0.2538</v>
       </c>
       <c r="J142" t="n">
-        <v>6.0312</v>
+        <v>6.0912</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.2088</v>
+        <v>-0.7824</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.78</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3682</v>
+        <v>-0.2403</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.8368</v>
+        <v>-5.7672</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4287</v>
+        <v>-0.2792</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.2888</v>
+        <v>-6.7008</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.68</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.3365</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.3264</v>
+        <v>-8.076000000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.58</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4193</v>
+        <v>1.2672</v>
       </c>
       <c r="J147" t="n">
-        <v>34.0632</v>
+        <v>30.4128</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.37</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9931</v>
+        <v>0.9759</v>
       </c>
       <c r="J148" t="n">
-        <v>23.8344</v>
+        <v>23.4216</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.11</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3195</v>
+        <v>0.3472</v>
       </c>
       <c r="J149" t="n">
-        <v>7.668</v>
+        <v>8.332800000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3621</v>
+        <v>-0.2931</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.6904</v>
+        <v>-7.0344</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.1293</v>
+        <v>-1.1213</v>
       </c>
       <c r="J151" t="n">
-        <v>-27.1032</v>
+        <v>-26.9112</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.54</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8099</v>
+        <v>1.0048</v>
       </c>
       <c r="J152" t="n">
-        <v>22.6772</v>
+        <v>28.1344</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.36</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.7211</v>
       </c>
       <c r="J153" t="n">
-        <v>16.7244</v>
+        <v>20.1908</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.8</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3831</v>
+        <v>-0.2388</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.7268</v>
+        <v>-6.6864</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5712</v>
+        <v>-0.3736</v>
       </c>
       <c r="J155" t="n">
-        <v>-15.9936</v>
+        <v>-10.4608</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.63</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6088</v>
+        <v>-0.4015</v>
       </c>
       <c r="J156" t="n">
-        <v>-17.0464</v>
+        <v>-11.242</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.21</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7317</v>
+        <v>0.6801</v>
       </c>
       <c r="J157" t="n">
-        <v>20.4876</v>
+        <v>19.0428</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.379</v>
+        <v>0.3146</v>
       </c>
       <c r="J158" t="n">
-        <v>10.612</v>
+        <v>8.8088</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3212</v>
+        <v>-0.3024</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.993600000000001</v>
+        <v>-8.4672</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6898</v>
+        <v>-0.6528</v>
       </c>
       <c r="J160" t="n">
-        <v>-19.3144</v>
+        <v>-18.2784</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.7</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8831</v>
+        <v>-0.8542</v>
       </c>
       <c r="J161" t="n">
-        <v>-24.7268</v>
+        <v>-23.9176</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5594</v>
+        <v>0.5112</v>
       </c>
       <c r="J162" t="n">
-        <v>15.6632</v>
+        <v>14.3136</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0531</v>
+        <v>-0.0606</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.4868</v>
+        <v>-1.6968</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>0.84</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2703</v>
+        <v>-0.1818</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.5684</v>
+        <v>-5.0904</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4737</v>
+        <v>-0.3088</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.2636</v>
+        <v>-8.6464</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7563</v>
+        <v>-0.5135</v>
       </c>
       <c r="J166" t="n">
-        <v>-21.1764</v>
+        <v>-14.378</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7583</v>
+        <v>0.6734</v>
       </c>
       <c r="J167" t="n">
-        <v>21.2324</v>
+        <v>18.8552</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.25</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4241</v>
+        <v>0.3576</v>
       </c>
       <c r="J168" t="n">
-        <v>11.8748</v>
+        <v>10.0128</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1443</v>
+        <v>-0.0722</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.0404</v>
+        <v>-2.0216</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.92</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.218</v>
+        <v>-0.1211</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.104</v>
+        <v>-3.3908</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4156</v>
+        <v>-0.2587</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.6368</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2363</v>
+        <v>1.145</v>
       </c>
       <c r="J172" t="n">
-        <v>28.4349</v>
+        <v>26.335</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.48</v>
       </c>
       <c r="I173" t="n">
-        <v>1.2363</v>
+        <v>1.145</v>
       </c>
       <c r="J173" t="n">
-        <v>28.4349</v>
+        <v>26.335</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.95</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2878</v>
+        <v>-0.2226</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.6194</v>
+        <v>-5.1198</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7008</v>
+        <v>-0.6481</v>
       </c>
       <c r="J175" t="n">
-        <v>-16.1184</v>
+        <v>-14.9063</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7958</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.3034</v>
+        <v>-17.2615</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5258</v>
+        <v>0.6216</v>
       </c>
       <c r="J177" t="n">
-        <v>12.0934</v>
+        <v>14.2968</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.95</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.046</v>
+        <v>-0.0578</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.058</v>
+        <v>-1.3294</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.82</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.297</v>
+        <v>-0.1999</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.831</v>
+        <v>-4.5977</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.483</v>
+        <v>-0.3161</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.109</v>
+        <v>-7.2703</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.47</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="J181" t="n">
-        <v>-17.8871</v>
+        <v>-12.1877</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.9</v>
       </c>
       <c r="I182" t="n">
-        <v>1.8694</v>
+        <v>1.5781</v>
       </c>
       <c r="J182" t="n">
-        <v>41.1268</v>
+        <v>34.7182</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.47</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0692</v>
+        <v>1.0697</v>
       </c>
       <c r="J183" t="n">
-        <v>23.5224</v>
+        <v>23.5334</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.31</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6807</v>
+        <v>0.7815</v>
       </c>
       <c r="J184" t="n">
-        <v>14.9754</v>
+        <v>17.193</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.31</v>
       </c>
       <c r="I185" t="n">
-        <v>0.6807</v>
+        <v>0.7815</v>
       </c>
       <c r="J185" t="n">
-        <v>14.9754</v>
+        <v>17.193</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.438</v>
+        <v>-0.356</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.635999999999999</v>
+        <v>-7.832</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>0.97</v>
       </c>
       <c r="I187" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0649</v>
       </c>
       <c r="J187" t="n">
-        <v>2.1274</v>
+        <v>1.4278</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>0.71</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3398</v>
+        <v>-0.2748</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.4756</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.52</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.6599</v>
+        <v>-0.4507</v>
       </c>
       <c r="J189" t="n">
-        <v>-14.5178</v>
+        <v>-9.9154</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.7155</v>
+        <v>-0.4884</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.741</v>
+        <v>-10.7448</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.44</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.769</v>
+        <v>-0.5262</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.918</v>
+        <v>-11.5764</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.46</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2186</v>
+        <v>1.132</v>
       </c>
       <c r="J192" t="n">
-        <v>34.1208</v>
+        <v>31.696</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.21</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6612</v>
+        <v>0.625</v>
       </c>
       <c r="J193" t="n">
-        <v>18.5136</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.17</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5584</v>
+        <v>0.5221</v>
       </c>
       <c r="J194" t="n">
-        <v>15.6352</v>
+        <v>14.6188</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.8298</v>
+        <v>-0.7893</v>
       </c>
       <c r="J195" t="n">
-        <v>-23.2344</v>
+        <v>-22.1004</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9649</v>
+        <v>-0.9373</v>
       </c>
       <c r="J196" t="n">
-        <v>-27.0172</v>
+        <v>-26.2444</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3669</v>
+        <v>0.4092</v>
       </c>
       <c r="J197" t="n">
-        <v>10.2732</v>
+        <v>11.4576</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0533</v>
       </c>
       <c r="J198" t="n">
-        <v>2.1756</v>
+        <v>1.4924</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2161</v>
+        <v>-0.137</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.0508</v>
+        <v>-3.836</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3483</v>
+        <v>-0.2198</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.7524</v>
+        <v>-6.1544</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4502</v>
+        <v>-0.2888</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.6056</v>
+        <v>-8.086399999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8766</v>
+        <v>0.8438</v>
       </c>
       <c r="J202" t="n">
-        <v>25.4214</v>
+        <v>24.4702</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>1.1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3897</v>
+        <v>0.3454</v>
       </c>
       <c r="J203" t="n">
-        <v>11.3013</v>
+        <v>10.0166</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.98</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1272</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.6888</v>
+        <v>-2.7753</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5689</v>
+        <v>-0.5184</v>
       </c>
       <c r="J205" t="n">
-        <v>-16.4981</v>
+        <v>-15.0336</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.84</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5689</v>
+        <v>-0.5184</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.4981</v>
+        <v>-15.0336</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3265</v>
+        <v>0.3658</v>
       </c>
       <c r="J207" t="n">
-        <v>9.468500000000001</v>
+        <v>10.6082</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2302</v>
+        <v>0.2479</v>
       </c>
       <c r="J208" t="n">
-        <v>6.6758</v>
+        <v>7.1891</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1118</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.2422</v>
+        <v>-1.8183</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1529</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.4341</v>
+        <v>-2.5375</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3677</v>
+        <v>-0.2283</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.6633</v>
+        <v>-6.6207</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.11</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4166</v>
+        <v>0.3726</v>
       </c>
       <c r="J212" t="n">
-        <v>11.2482</v>
+        <v>10.0602</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.02</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1027</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>2.7729</v>
+        <v>2.4516</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0457</v>
+        <v>0.0514</v>
       </c>
       <c r="J214" t="n">
-        <v>1.2339</v>
+        <v>1.3878</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1714</v>
+        <v>-0.1333</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.6278</v>
+        <v>-3.5991</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2093</v>
+        <v>-0.1679</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.6511</v>
+        <v>-4.5333</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.13</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2982</v>
+        <v>0.3233</v>
       </c>
       <c r="J217" t="n">
-        <v>8.051399999999999</v>
+        <v>8.729100000000001</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.02</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0946</v>
+        <v>0.0775</v>
       </c>
       <c r="J218" t="n">
-        <v>2.5542</v>
+        <v>2.0925</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.95</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0988</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.6676</v>
+        <v>-1.9278</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1488</v>
+        <v>-0.0946</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.0176</v>
+        <v>-2.5542</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5225</v>
+        <v>-0.3392</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.1075</v>
+        <v>-9.1584</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.39</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0457</v>
+        <v>1.0177</v>
       </c>
       <c r="J222" t="n">
-        <v>23.0054</v>
+        <v>22.3894</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.38</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0243</v>
+        <v>1.0007</v>
       </c>
       <c r="J223" t="n">
-        <v>22.5346</v>
+        <v>22.0154</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7785</v>
       </c>
       <c r="J224" t="n">
-        <v>17.6198</v>
+        <v>17.127</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>-17.0434</v>
+        <v>-16.0006</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9556</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="J226" t="n">
-        <v>-21.0232</v>
+        <v>-20.3698</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4793</v>
+        <v>0.5567</v>
       </c>
       <c r="J227" t="n">
-        <v>10.5446</v>
+        <v>12.2474</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2236</v>
+        <v>-0.162</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.9192</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3217</v>
+        <v>-0.2113</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.0774</v>
+        <v>-4.6486</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3217</v>
+        <v>-0.2113</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.0774</v>
+        <v>-4.6486</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6707</v>
+        <v>-0.4492</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.7554</v>
+        <v>-9.882400000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>2.01</v>
       </c>
       <c r="I232" t="n">
-        <v>2.0088</v>
+        <v>1.7161</v>
       </c>
       <c r="J232" t="n">
-        <v>42.1848</v>
+        <v>36.0381</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.44</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0274</v>
+        <v>1.0369</v>
       </c>
       <c r="J233" t="n">
-        <v>21.5754</v>
+        <v>21.7749</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.34</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7844</v>
+        <v>0.8536</v>
       </c>
       <c r="J234" t="n">
-        <v>16.4724</v>
+        <v>17.9256</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.07</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0953</v>
+        <v>0.1814</v>
       </c>
       <c r="J235" t="n">
-        <v>2.0013</v>
+        <v>3.8094</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6408</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.4568</v>
+        <v>-12.0771</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>0.86</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1168</v>
+        <v>-0.1199</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.4528</v>
+        <v>-2.5179</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>0.78</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2447</v>
+        <v>-0.2091</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.1387</v>
+        <v>-4.3911</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4404</v>
+        <v>-0.3275</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.2484</v>
+        <v>-6.8775</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.5</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.4742</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.6391</v>
+        <v>-9.9582</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7634</v>
+        <v>-0.5214</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.0314</v>
+        <v>-10.9494</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8524</v>
+        <v>0.8235</v>
       </c>
       <c r="J242" t="n">
-        <v>28.9816</v>
+        <v>27.999</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8061</v>
+        <v>0.7746</v>
       </c>
       <c r="J243" t="n">
-        <v>27.4074</v>
+        <v>26.3364</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0553</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>1.8802</v>
+        <v>2.8594</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.86</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5334</v>
+        <v>-0.4764</v>
       </c>
       <c r="J245" t="n">
-        <v>-18.1356</v>
+        <v>-16.1976</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6372</v>
+        <v>-0.584</v>
       </c>
       <c r="J246" t="n">
-        <v>-21.6648</v>
+        <v>-19.856</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.22</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4523</v>
+        <v>0.5204</v>
       </c>
       <c r="J247" t="n">
-        <v>15.3782</v>
+        <v>17.6936</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2186</v>
+        <v>0.2163</v>
       </c>
       <c r="J248" t="n">
-        <v>7.4324</v>
+        <v>7.3542</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.99</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0231</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>0.7854</v>
+        <v>-0.2788</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.67</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5367</v>
+        <v>-0.3511</v>
       </c>
       <c r="J250" t="n">
-        <v>-18.2478</v>
+        <v>-11.9374</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.49</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7612</v>
+        <v>-0.5172</v>
       </c>
       <c r="J251" t="n">
-        <v>-25.8808</v>
+        <v>-17.5848</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.5</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2905</v>
+        <v>1.1802</v>
       </c>
       <c r="J252" t="n">
-        <v>36.134</v>
+        <v>33.0456</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.16</v>
+        <v>0.1835</v>
       </c>
       <c r="J253" t="n">
-        <v>4.48</v>
+        <v>5.138</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2049</v>
+        <v>-0.1474</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.7372</v>
+        <v>-4.1272</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4004</v>
+        <v>-0.3391</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.2112</v>
+        <v>-9.4948</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4004</v>
+        <v>-0.3391</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.2112</v>
+        <v>-9.4948</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0772</v>
+        <v>0.0398</v>
       </c>
       <c r="J257" t="n">
-        <v>2.1616</v>
+        <v>1.1144</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.95</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0469</v>
+        <v>-0.0582</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.3132</v>
+        <v>-1.6296</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.8</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3326</v>
+        <v>-0.2197</v>
       </c>
       <c r="J259" t="n">
-        <v>-9.312799999999999</v>
+        <v>-6.1516</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.75</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4111</v>
+        <v>-0.2684</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.5108</v>
+        <v>-7.5152</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.71</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4694</v>
+        <v>-0.3069</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.1432</v>
+        <v>-8.5932</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.89</v>
       </c>
       <c r="I262" t="n">
-        <v>1.898</v>
+        <v>1.5994</v>
       </c>
       <c r="J262" t="n">
-        <v>41.756</v>
+        <v>35.1868</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.63</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4408</v>
+        <v>1.287</v>
       </c>
       <c r="J263" t="n">
-        <v>31.6976</v>
+        <v>28.314</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4197</v>
+        <v>0.4984</v>
       </c>
       <c r="J264" t="n">
-        <v>9.2334</v>
+        <v>10.9648</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3807</v>
+        <v>-0.2997</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.375400000000001</v>
+        <v>-6.5934</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.71</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9151</v>
       </c>
       <c r="J266" t="n">
-        <v>-20.8362</v>
+        <v>-20.1322</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0035</v>
+        <v>-0.0366</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.077</v>
+        <v>-0.8052</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1634</v>
+        <v>-0.1452</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.5948</v>
+        <v>-3.1944</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3507</v>
+        <v>-0.2569</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.7154</v>
+        <v>-5.6518</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6188</v>
+        <v>-0.415</v>
       </c>
       <c r="J270" t="n">
-        <v>-13.6136</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6188</v>
+        <v>-0.415</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.6136</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>2.03</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0342</v>
+        <v>1.7488</v>
       </c>
       <c r="J272" t="n">
-        <v>40.684</v>
+        <v>34.976</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.75</v>
       </c>
       <c r="I273" t="n">
-        <v>1.6419</v>
+        <v>1.4213</v>
       </c>
       <c r="J273" t="n">
-        <v>32.838</v>
+        <v>28.426</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.07</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1046</v>
+        <v>0.1883</v>
       </c>
       <c r="J274" t="n">
-        <v>2.092</v>
+        <v>3.766</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5844</v>
+        <v>-0.5143</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.688</v>
+        <v>-10.286</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6592</v>
+        <v>-0.5956</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.184</v>
+        <v>-11.912</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1565</v>
+        <v>0.1286</v>
       </c>
       <c r="J277" t="n">
-        <v>3.13</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.96</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0193</v>
+        <v>-0.0211</v>
       </c>
       <c r="J278" t="n">
-        <v>0.386</v>
+        <v>-0.422</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.6</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5898</v>
+        <v>-0.3954</v>
       </c>
       <c r="J279" t="n">
-        <v>-11.796</v>
+        <v>-7.908</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6438</v>
+        <v>-0.4328</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.876</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6438</v>
+        <v>-0.4328</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.876</v>
+        <v>-8.656000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.48</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1879</v>
+        <v>1.1187</v>
       </c>
       <c r="J282" t="n">
-        <v>30.8854</v>
+        <v>29.0862</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>1.36</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9327</v>
       </c>
       <c r="J283" t="n">
-        <v>24.31</v>
+        <v>24.2502</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J284" t="n">
-        <v>20.7714</v>
+        <v>20.7194</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>1.03</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0198</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J285" t="n">
-        <v>0.5148</v>
+        <v>2.275</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.797</v>
+        <v>-0.7488</v>
       </c>
       <c r="J286" t="n">
-        <v>-20.722</v>
+        <v>-19.4688</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1</v>
+        <v>0.0622</v>
       </c>
       <c r="J287" t="n">
-        <v>2.6</v>
+        <v>1.6172</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0232</v>
+        <v>-0.0474</v>
       </c>
       <c r="J288" t="n">
-        <v>-0.6032</v>
+        <v>-1.2324</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2538</v>
+        <v>-0.195</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.5988</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3107</v>
+        <v>-0.224</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.078200000000001</v>
+        <v>-5.824</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.38</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.8756</v>
+        <v>-0.6057</v>
       </c>
       <c r="J291" t="n">
-        <v>-22.7656</v>
+        <v>-15.7482</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.12</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2545</v>
+        <v>0.282</v>
       </c>
       <c r="J292" t="n">
-        <v>7.635</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2379</v>
+        <v>0.2622</v>
       </c>
       <c r="J293" t="n">
-        <v>7.137</v>
+        <v>7.866</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0555</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J294" t="n">
-        <v>1.665</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1618</v>
+        <v>-0.09</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.854</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.9</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2334</v>
+        <v>-0.1362</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.002</v>
+        <v>-4.086</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.15</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5528</v>
+        <v>0.4986</v>
       </c>
       <c r="J297" t="n">
-        <v>16.584</v>
+        <v>14.958</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.11</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4418</v>
+        <v>0.3867</v>
       </c>
       <c r="J298" t="n">
-        <v>13.254</v>
+        <v>11.601</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.04</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2181</v>
+        <v>0.1713</v>
       </c>
       <c r="J299" t="n">
-        <v>6.543</v>
+        <v>5.139</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>0.88</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4417</v>
+        <v>-0.3987</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.251</v>
+        <v>-11.961</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.7</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8974</v>
+        <v>-0.8667</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.922</v>
+        <v>-26.001</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>0.99</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0655</v>
+        <v>0.0219</v>
       </c>
       <c r="J302" t="n">
-        <v>1.3755</v>
+        <v>0.4599</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0798</v>
+        <v>-0.0853</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.6758</v>
+        <v>-1.7913</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2364</v>
+        <v>-0.1849</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.9644</v>
+        <v>-3.8829</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.68</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4944</v>
+        <v>-0.3278</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.3824</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7074</v>
+        <v>-0.4773</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.8554</v>
+        <v>-10.0233</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.34</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8872</v>
+        <v>0.8868</v>
       </c>
       <c r="J307" t="n">
-        <v>18.6312</v>
+        <v>18.6228</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.26</v>
       </c>
       <c r="I308" t="n">
-        <v>0.6989</v>
+        <v>0.7023</v>
       </c>
       <c r="J308" t="n">
-        <v>14.6769</v>
+        <v>14.7483</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.595</v>
+        <v>0.6081</v>
       </c>
       <c r="J309" t="n">
-        <v>12.495</v>
+        <v>12.7701</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.17</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4387</v>
+        <v>0.4888</v>
       </c>
       <c r="J310" t="n">
-        <v>9.2127</v>
+        <v>10.2648</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.98</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2215</v>
+        <v>-0.1432</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.6515</v>
+        <v>-3.0072</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1986/event_1986_evp_summary.xlsx
+++ b/database/event/1986/event_1986_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.554</v>
+        <v>6.6558</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9047</v>
+        <v>3.9653</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3208</v>
+        <v>2.4057</v>
       </c>
       <c r="E2" t="n">
-        <v>6.554</v>
+        <v>6.6558</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1022</v>
+        <v>2.0751</v>
       </c>
       <c r="H2" t="n">
-        <v>13.0205</v>
+        <v>12.4233</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7701</v>
+        <v>6.7085</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1022</v>
+        <v>2.0751</v>
       </c>
       <c r="K2" t="n">
         <v>189</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>8.872299999999999</v>
+        <v>8.7836</v>
       </c>
       <c r="N2" t="n">
         <v>388</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8206</v>
+        <v>5.7619</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4677</v>
+        <v>3.4328</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9897</v>
+        <v>1.9987</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8206</v>
+        <v>5.7619</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7065</v>
+        <v>3.6439</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1141</v>
+        <v>2.118</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5732</v>
+        <v>7.1283</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9377</v>
+        <v>3.8492</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1141</v>
+        <v>2.118</v>
       </c>
       <c r="K3" t="n">
         <v>149</v>
@@ -575,7 +575,7 @@
         <v>192</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0518</v>
+        <v>5.9672</v>
       </c>
       <c r="N3" t="n">
         <v>341</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4119</v>
+        <v>4.4349</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6285</v>
+        <v>2.6422</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3537</v>
+        <v>1.3947</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4119</v>
+        <v>4.4349</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4093</v>
+        <v>3.3476</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0026</v>
+        <v>1.0873</v>
       </c>
       <c r="H4" t="n">
-        <v>6.526</v>
+        <v>6.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3932</v>
+        <v>3.3213</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0026</v>
+        <v>1.0873</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
@@ -621,7 +621,7 @@
         <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3958</v>
+        <v>4.4086</v>
       </c>
       <c r="N4" t="n">
         <v>165</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4737</v>
+        <v>3.4321</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0695</v>
+        <v>2.0447</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9302</v>
+        <v>0.9382</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4737</v>
+        <v>3.4321</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2245</v>
+        <v>3.1349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2492</v>
+        <v>0.2972</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8747</v>
+        <v>5.4492</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0546</v>
+        <v>2.9425</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2492</v>
+        <v>0.2972</v>
       </c>
       <c r="K5" t="n">
         <v>189</v>
@@ -667,7 +667,7 @@
         <v>199</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3038</v>
+        <v>3.2397</v>
       </c>
       <c r="N5" t="n">
         <v>388</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.956</v>
+        <v>2.6134</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7611</v>
+        <v>1.557</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6965</v>
+        <v>0.5655</v>
       </c>
       <c r="E6" t="n">
-        <v>2.956</v>
+        <v>2.6134</v>
       </c>
       <c r="F6" t="n">
-        <v>2.956</v>
+        <v>1.6189</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1311</v>
+        <v>1.6189</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1311</v>
+        <v>0.8742</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1311</v>
+        <v>1.8687</v>
       </c>
       <c r="N6" t="n">
-        <v>178</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6581</v>
+        <v>2.6037</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5836</v>
+        <v>1.5512</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5611</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6581</v>
+        <v>2.6037</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7336</v>
+        <v>2.6037</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9245</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7336</v>
+        <v>2.9737</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9014</v>
+        <v>2.9737</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9245</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="L7" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8259</v>
+        <v>2.9737</v>
       </c>
       <c r="N7" t="n">
-        <v>388</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5164</v>
+        <v>2.4032</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4992</v>
+        <v>1.4318</v>
       </c>
       <c r="D8" t="n">
-        <v>0.498</v>
+        <v>0.4698</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5164</v>
+        <v>2.4032</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1615</v>
+        <v>3.0734</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6451</v>
+        <v>-0.6702</v>
       </c>
       <c r="H8" t="n">
-        <v>5.653</v>
+        <v>5.246</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9393</v>
+        <v>2.8328</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6451</v>
+        <v>-0.6702</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -805,7 +805,7 @@
         <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2942</v>
+        <v>2.1626</v>
       </c>
       <c r="N8" t="n">
         <v>165</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5077</v>
+        <v>2.3124</v>
       </c>
       <c r="C9" t="n">
-        <v>1.494</v>
+        <v>1.3777</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4941</v>
+        <v>0.4284</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5077</v>
+        <v>2.3124</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5077</v>
+        <v>2.3124</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5077</v>
+        <v>2.3362</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5077</v>
+        <v>2.3362</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5077</v>
+        <v>2.3362</v>
       </c>
       <c r="N9" t="n">
         <v>184</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.413</v>
+        <v>2.2803</v>
       </c>
       <c r="C10" t="n">
-        <v>1.4376</v>
+        <v>1.3585</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4513</v>
+        <v>0.4138</v>
       </c>
       <c r="E10" t="n">
-        <v>2.413</v>
+        <v>2.2803</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6154</v>
+        <v>2.5117</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2024</v>
+        <v>-0.2314</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7288</v>
+        <v>3.3928</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9388</v>
+        <v>1.8321</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2024</v>
+        <v>-0.2314</v>
       </c>
       <c r="K10" t="n">
         <v>100</v>
@@ -897,7 +897,7 @@
         <v>65</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7364</v>
+        <v>1.6007</v>
       </c>
       <c r="N10" t="n">
         <v>165</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.257</v>
+        <v>2.1184</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3447</v>
+        <v>1.2621</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3809</v>
+        <v>0.3401</v>
       </c>
       <c r="E11" t="n">
-        <v>2.257</v>
+        <v>2.1184</v>
       </c>
       <c r="F11" t="n">
-        <v>2.257</v>
+        <v>2.1184</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.257</v>
+        <v>2.1184</v>
       </c>
       <c r="I11" t="n">
-        <v>2.257</v>
+        <v>2.1184</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.257</v>
+        <v>2.1184</v>
       </c>
       <c r="N11" t="n">
         <v>178</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1638</v>
+        <v>2.038</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2891</v>
+        <v>1.2142</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3388</v>
+        <v>0.3035</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1638</v>
+        <v>2.038</v>
       </c>
       <c r="F12" t="n">
-        <v>2.297</v>
+        <v>2.1823</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1332</v>
+        <v>-0.1443</v>
       </c>
       <c r="H12" t="n">
-        <v>2.607</v>
+        <v>2.306</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3555</v>
+        <v>1.2452</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1332</v>
+        <v>-0.1443</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2223</v>
+        <v>1.1009</v>
       </c>
       <c r="N12" t="n">
         <v>165</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0676</v>
+        <v>1.9679</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2318</v>
+        <v>1.1724</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2954</v>
+        <v>0.2716</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0676</v>
+        <v>1.9679</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6501</v>
+        <v>1.5391</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4175</v>
+        <v>0.4288</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6501</v>
+        <v>1.5391</v>
       </c>
       <c r="I13" t="n">
-        <v>0.858</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4175</v>
+        <v>0.4288</v>
       </c>
       <c r="K13" t="n">
         <v>100</v>
@@ -1035,7 +1035,7 @@
         <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2755</v>
+        <v>1.2599</v>
       </c>
       <c r="N13" t="n">
         <v>165</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1046</v>
+        <v>1.1202</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6581</v>
+        <v>0.6674</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1393</v>
+        <v>-0.1143</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1046</v>
+        <v>1.1202</v>
       </c>
       <c r="F14" t="n">
-        <v>2.779</v>
+        <v>2.7104</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6744</v>
+        <v>-1.5902</v>
       </c>
       <c r="H14" t="n">
-        <v>4.305</v>
+        <v>4.0486</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2384</v>
+        <v>2.1862</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.6744</v>
+        <v>-1.5902</v>
       </c>
       <c r="K14" t="n">
         <v>149</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5639999999999998</v>
+        <v>0.5959999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>341</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7529</v>
+        <v>0.6472</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4486</v>
+        <v>0.3856</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2981</v>
+        <v>-0.3296</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7529</v>
+        <v>0.6472</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7529</v>
+        <v>0.6472</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7529</v>
+        <v>0.6472</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7529</v>
+        <v>0.6472</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7529</v>
+        <v>0.6472</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5997</v>
+        <v>0.554</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3573</v>
+        <v>0.3301</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3673</v>
+        <v>-0.372</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5997</v>
+        <v>0.554</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5997</v>
+        <v>0.318</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5997</v>
+        <v>0.318</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5997</v>
+        <v>0.1717</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="K16" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5997</v>
+        <v>0.4077</v>
       </c>
       <c r="N16" t="n">
-        <v>102</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5569</v>
+        <v>0.539</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3318</v>
+        <v>0.3211</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3866</v>
+        <v>-0.3788</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5569</v>
+        <v>0.539</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3135</v>
+        <v>0.539</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2434</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3135</v>
+        <v>0.539</v>
       </c>
       <c r="I17" t="n">
-        <v>0.163</v>
+        <v>0.539</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2434</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L17" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4064</v>
+        <v>0.539</v>
       </c>
       <c r="N17" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>mOE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3532</v>
+        <v>0.2687</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2104</v>
+        <v>0.1601</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4786</v>
+        <v>-0.5019</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3532</v>
+        <v>0.2687</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3532</v>
+        <v>0.2687</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3532</v>
+        <v>0.2687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3532</v>
+        <v>0.2687</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3532</v>
+        <v>0.2687</v>
       </c>
       <c r="N18" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.297</v>
+        <v>0.2664</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1769</v>
+        <v>0.1587</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5039</v>
+        <v>-0.5029</v>
       </c>
       <c r="E19" t="n">
-        <v>0.297</v>
+        <v>0.2664</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9043</v>
+        <v>0.8996</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6073</v>
+        <v>-0.6332</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9043</v>
+        <v>0.8996</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4702</v>
+        <v>0.4858</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6073</v>
+        <v>-0.6332</v>
       </c>
       <c r="K19" t="n">
         <v>100</v>
@@ -1311,7 +1311,7 @@
         <v>65</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1370999999999999</v>
+        <v>-0.1474</v>
       </c>
       <c r="N19" t="n">
         <v>165</v>
@@ -1320,231 +1320,231 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mOE</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2841</v>
+        <v>0.2545</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1693</v>
+        <v>0.1516</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5098</v>
+        <v>-0.5083</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2841</v>
+        <v>0.2545</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2841</v>
+        <v>0.2545</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2841</v>
+        <v>0.2545</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2841</v>
+        <v>0.2545</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2841</v>
+        <v>0.2545</v>
       </c>
       <c r="N20" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2117</v>
+        <v>0.0888</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1261</v>
+        <v>0.0529</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5424</v>
+        <v>-0.5838</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2117</v>
+        <v>0.0888</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2117</v>
+        <v>0.5798</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.491</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2117</v>
+        <v>0.5798</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2117</v>
+        <v>0.3131</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.491</v>
       </c>
       <c r="K21" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2117</v>
+        <v>-0.1779</v>
       </c>
       <c r="N21" t="n">
-        <v>119</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1686</v>
+        <v>0.0798</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1004</v>
+        <v>0.0475</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5619</v>
+        <v>-0.5879</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1686</v>
+        <v>0.0798</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6506</v>
+        <v>0.0798</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.482</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6506</v>
+        <v>0.0798</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3383</v>
+        <v>0.0798</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.482</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1437</v>
+        <v>0.0798</v>
       </c>
       <c r="N22" t="n">
-        <v>341</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0743</v>
+        <v>-0.1041</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0443</v>
+        <v>-0.062</v>
       </c>
       <c r="D23" t="n">
         <v>-0.6716</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0743</v>
+        <v>-0.1041</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0743</v>
+        <v>-0.1041</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0743</v>
+        <v>-0.1041</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0743</v>
+        <v>-0.1041</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0743</v>
+        <v>-0.1041</v>
       </c>
       <c r="N23" t="n">
-        <v>184</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0696</v>
+        <v>-0.0701</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6908</v>
+        <v>-0.6778</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="N24" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3738</v>
+        <v>-0.2712</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.2227</v>
+        <v>-0.1616</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8068</v>
+        <v>-0.7477</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3738</v>
+        <v>-0.2712</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8307</v>
+        <v>-0.7383</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4569</v>
+        <v>0.4671</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8307</v>
+        <v>-0.7383</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4319</v>
+        <v>-0.3987</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4569</v>
+        <v>0.4671</v>
       </c>
       <c r="K25" t="n">
         <v>149</v>
@@ -1587,7 +1587,7 @@
         <v>192</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02499999999999997</v>
+        <v>0.06840000000000002</v>
       </c>
       <c r="N25" t="n">
         <v>341</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5011</v>
+        <v>-0.5283</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2985</v>
+        <v>-0.3147</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8642</v>
+        <v>-0.8647</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5011</v>
+        <v>-0.5283</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3358</v>
+        <v>-0.3641</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1653</v>
+        <v>-0.1642</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3358</v>
+        <v>-0.3641</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1746</v>
+        <v>-0.1966</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1653</v>
+        <v>-0.1642</v>
       </c>
       <c r="K26" t="n">
         <v>149</v>
@@ -1633,7 +1633,7 @@
         <v>192</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3399</v>
+        <v>-0.3608</v>
       </c>
       <c r="N26" t="n">
         <v>341</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5329</v>
+        <v>-0.5974</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3175</v>
+        <v>-0.3559</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8786</v>
+        <v>-0.8962</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5329</v>
+        <v>-0.5974</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5329</v>
+        <v>-0.5974</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5329</v>
+        <v>-0.5974</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5329</v>
+        <v>-0.5974</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5329</v>
+        <v>-0.5974</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5491</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3271</v>
+        <v>-0.3781</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8859</v>
+        <v>-0.9131</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5491</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5491</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5491</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5491</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5491</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6363</v>
+        <v>-0.7006</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3791</v>
+        <v>-0.4174</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9253</v>
+        <v>-0.9431</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6363</v>
+        <v>-0.7006</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6363</v>
+        <v>-0.7006</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6363</v>
+        <v>-0.7006</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6363</v>
+        <v>-0.7006</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6363</v>
+        <v>-0.7006</v>
       </c>
       <c r="N29" t="n">
         <v>102</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.9563</v>
+        <v>-1.004</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5697</v>
+        <v>-0.5982</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0697</v>
+        <v>-1.0812</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.9563</v>
+        <v>-1.004</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.9563</v>
+        <v>-1.004</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9563</v>
+        <v>-1.004</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9563</v>
+        <v>-1.004</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.9563</v>
+        <v>-1.004</v>
       </c>
       <c r="N30" t="n">
         <v>184</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0242</v>
+        <v>-1.0848</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6102</v>
+        <v>-0.6463</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1004</v>
+        <v>-1.118</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0242</v>
+        <v>-1.0848</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0242</v>
+        <v>-1.0848</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0242</v>
+        <v>-1.0848</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0242</v>
+        <v>-1.0848</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0242</v>
+        <v>-1.0848</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.1082</v>
+        <v>-1.1719</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.6602</v>
+        <v>-0.6982</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.1383</v>
+        <v>-1.1577</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.1082</v>
+        <v>-1.1719</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1082</v>
+        <v>-1.1719</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1082</v>
+        <v>-1.1719</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.1082</v>
+        <v>-1.1719</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.1082</v>
+        <v>-1.1719</v>
       </c>
       <c r="N32" t="n">
         <v>178</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2099</v>
+        <v>-1.2779</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.7208</v>
+        <v>-0.7613</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.1842</v>
+        <v>-1.2059</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2099</v>
+        <v>-1.2779</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2099</v>
+        <v>-1.2779</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.2099</v>
+        <v>-1.2779</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.2099</v>
+        <v>-1.2779</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.2099</v>
+        <v>-1.2779</v>
       </c>
       <c r="N33" t="n">
         <v>119</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2973</v>
+        <v>-1.356</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.7729</v>
+        <v>-0.8079</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.2237</v>
+        <v>-1.2415</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2973</v>
+        <v>-1.356</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.2973</v>
+        <v>-1.356</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.2973</v>
+        <v>-1.356</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.2973</v>
+        <v>-1.356</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2973</v>
+        <v>-1.356</v>
       </c>
       <c r="N34" t="n">
         <v>102</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3668</v>
+        <v>-1.3837</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.8143</v>
+        <v>-0.8244</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.2551</v>
+        <v>-1.2541</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3668</v>
+        <v>-1.3837</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3668</v>
+        <v>-1.3837</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3668</v>
+        <v>-1.3837</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3668</v>
+        <v>-1.3837</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3668</v>
+        <v>-1.3837</v>
       </c>
       <c r="N35" t="n">
         <v>178</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.623</v>
+        <v>-1.6317</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.9669</v>
+        <v>-0.9721</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.3707</v>
+        <v>-1.367</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.623</v>
+        <v>-1.6317</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.623</v>
+        <v>-1.6317</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.623</v>
+        <v>-1.6317</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.623</v>
+        <v>-1.6317</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.623</v>
+        <v>-1.6317</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.0888</v>
+        <v>-1.8279</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.2444</v>
+        <v>-1.089</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.581</v>
+        <v>-1.4563</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.0888</v>
+        <v>-1.8279</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.7909</v>
+        <v>-1.4978</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2979</v>
+        <v>-0.3301</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.7909</v>
+        <v>-1.4978</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9312</v>
+        <v>-0.8088</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2979</v>
+        <v>-0.3301</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
@@ -2139,7 +2139,7 @@
         <v>65</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2291</v>
+        <v>-1.1389</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.1045</v>
+        <v>-2.0353</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.2538</v>
+        <v>-1.2126</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5881</v>
+        <v>-1.5507</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.1045</v>
+        <v>-2.0353</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5684</v>
+        <v>-1.4843</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5361</v>
+        <v>-0.551</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5684</v>
+        <v>-1.4843</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8155</v>
+        <v>-0.8015</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5361</v>
+        <v>-0.551</v>
       </c>
       <c r="K38" t="n">
         <v>189</v>
@@ -2185,7 +2185,7 @@
         <v>199</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3516</v>
+        <v>-1.3525</v>
       </c>
       <c r="N38" t="n">
         <v>388</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.4296</v>
+        <v>-2.2308</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.4475</v>
+        <v>-1.329</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.7349</v>
+        <v>-1.6397</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.4296</v>
+        <v>-2.2308</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.0823</v>
+        <v>-1.8548</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.3473</v>
+        <v>-0.376</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.0823</v>
+        <v>-1.8548</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0827</v>
+        <v>-1.0016</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.3473</v>
+        <v>-0.376</v>
       </c>
       <c r="K39" t="n">
         <v>107</v>
@@ -2231,7 +2231,7 @@
         <v>58</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.43</v>
+        <v>-1.3776</v>
       </c>
       <c r="N39" t="n">
         <v>165</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.9755</v>
+        <v>-3.5639</v>
       </c>
       <c r="C40" t="n">
-        <v>-2.3685</v>
+        <v>-2.1233</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.4328</v>
+        <v>-2.2466</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.9755</v>
+        <v>-3.5639</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.9755</v>
+        <v>-3.6006</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.9755</v>
+        <v>-3.6006</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.9755</v>
+        <v>-1.9443</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.0367</v>
       </c>
       <c r="K40" t="n">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.9755</v>
+        <v>-1.9076</v>
       </c>
       <c r="N40" t="n">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.0048</v>
+        <v>-3.8133</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.3859</v>
+        <v>-2.2719</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.446</v>
+        <v>-2.3601</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.0048</v>
+        <v>-3.8133</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.0302</v>
+        <v>-3.8133</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0254</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.0302</v>
+        <v>-3.8133</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0955</v>
+        <v>-3.8133</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0254</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="L41" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0701</v>
+        <v>-3.8133</v>
       </c>
       <c r="N41" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42">
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-4.7916</v>
+        <v>-4.3901</v>
       </c>
       <c r="C42" t="n">
-        <v>-2.8547</v>
+        <v>-2.6155</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.8012</v>
+        <v>-2.6227</v>
       </c>
       <c r="E42" t="n">
-        <v>-4.7916</v>
+        <v>-4.3901</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.9661</v>
+        <v>-3.5806</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.8255</v>
+        <v>-0.8095</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.9661</v>
+        <v>-3.5806</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.0622</v>
+        <v>-1.9335</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8255</v>
+        <v>-0.8095</v>
       </c>
       <c r="K42" t="n">
         <v>189</v>
@@ -2369,7 +2369,7 @@
         <v>199</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.8877</v>
+        <v>-2.743</v>
       </c>
       <c r="N42" t="n">
         <v>388</v>
@@ -2475,10 +2475,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9427</v>
+        <v>0.8712</v>
       </c>
       <c r="J2" t="n">
-        <v>28.281</v>
+        <v>26.136</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3761</v>
+        <v>0.3672</v>
       </c>
       <c r="J3" t="n">
-        <v>11.283</v>
+        <v>11.016</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.015</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0003</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.015</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1638</v>
+        <v>-1.0587</v>
       </c>
       <c r="J6" t="n">
-        <v>-34.914</v>
+        <v>-31.761</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9382</v>
+        <v>0.884</v>
       </c>
       <c r="J7" t="n">
-        <v>28.146</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2772</v>
+        <v>0.2796</v>
       </c>
       <c r="J8" t="n">
-        <v>8.316000000000001</v>
+        <v>8.388</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.141</v>
+        <v>-0.1549</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.23</v>
+        <v>-4.647</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1939</v>
+        <v>-0.2084</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.817</v>
+        <v>-6.252</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.49</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5248</v>
+        <v>-0.5286</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.744</v>
+        <v>-15.858</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0441</v>
+        <v>0.9828</v>
       </c>
       <c r="J12" t="n">
-        <v>31.323</v>
+        <v>29.484</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2949</v>
+        <v>0.291</v>
       </c>
       <c r="J13" t="n">
-        <v>8.847</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.724</v>
+        <v>-2.928</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3158</v>
+        <v>-0.3124</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.474</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.58</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1591</v>
+        <v>-1.0553</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.773</v>
+        <v>-31.659</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3607</v>
+        <v>0.3577</v>
       </c>
       <c r="J17" t="n">
-        <v>10.821</v>
+        <v>10.731</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0166</v>
+        <v>-0.0222</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.498</v>
+        <v>-0.666</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0835</v>
+        <v>-0.0955</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.505</v>
+        <v>-2.865</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1065</v>
+        <v>-0.1197</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.195</v>
+        <v>-3.591</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2824</v>
+        <v>-0.2963</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.472</v>
+        <v>-8.888999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.11</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2615</v>
+        <v>0.2562</v>
       </c>
       <c r="J22" t="n">
-        <v>5.753</v>
+        <v>5.6364</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0214</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1848</v>
+        <v>-0.4708</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1969</v>
+        <v>-0.2155</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.3318</v>
+        <v>-4.741</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.67</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3395</v>
+        <v>-0.3554</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.469</v>
+        <v>-7.8188</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.44</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5575</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.1638</v>
+        <v>-12.265</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5219</v>
       </c>
       <c r="J27" t="n">
-        <v>11.2992</v>
+        <v>11.4818</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.24</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3293</v>
+        <v>0.3457</v>
       </c>
       <c r="J28" t="n">
-        <v>7.2446</v>
+        <v>7.6054</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2457</v>
+        <v>0.2634</v>
       </c>
       <c r="J29" t="n">
-        <v>5.4054</v>
+        <v>5.7948</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1666</v>
+        <v>0.1847</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6652</v>
+        <v>4.0634</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>1.06</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0931</v>
+        <v>0.1099</v>
       </c>
       <c r="J31" t="n">
-        <v>2.0482</v>
+        <v>2.4178</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1561</v>
+        <v>0.1617</v>
       </c>
       <c r="J32" t="n">
-        <v>4.683</v>
+        <v>4.851</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>0.97</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0436</v>
+        <v>-0.0533</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.308</v>
+        <v>-1.599</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1064</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.799</v>
+        <v>-3.192</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1262</v>
+        <v>-0.1407</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.786</v>
+        <v>-4.221</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2791</v>
+        <v>-0.2938</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.372999999999999</v>
+        <v>-8.814</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.31</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4469</v>
+        <v>0.4519</v>
       </c>
       <c r="J37" t="n">
-        <v>13.407</v>
+        <v>13.557</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2556</v>
+        <v>0.2678</v>
       </c>
       <c r="J38" t="n">
-        <v>7.668</v>
+        <v>8.034000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2285</v>
+        <v>0.2411</v>
       </c>
       <c r="J39" t="n">
-        <v>6.855</v>
+        <v>7.233</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3</v>
+        <v>-0.312</v>
       </c>
       <c r="J40" t="n">
-        <v>-9</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3</v>
+        <v>-0.312</v>
       </c>
       <c r="J41" t="n">
-        <v>-9</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.51</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1408</v>
+        <v>1.1421</v>
       </c>
       <c r="J42" t="n">
-        <v>25.0976</v>
+        <v>25.1262</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.36</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9127</v>
+        <v>0.8607</v>
       </c>
       <c r="J43" t="n">
-        <v>20.0794</v>
+        <v>18.9354</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.35</v>
       </c>
       <c r="I44" t="n">
-        <v>0.891</v>
+        <v>0.8413</v>
       </c>
       <c r="J44" t="n">
-        <v>19.602</v>
+        <v>18.5086</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3982</v>
+        <v>0.401</v>
       </c>
       <c r="J45" t="n">
-        <v>8.760400000000001</v>
+        <v>8.821999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.93</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3281</v>
+        <v>-0.3071</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.2182</v>
+        <v>-6.7562</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3529</v>
+        <v>0.3164</v>
       </c>
       <c r="J47" t="n">
-        <v>7.7638</v>
+        <v>6.9608</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.59</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3908</v>
+        <v>-0.4087</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.5976</v>
+        <v>-8.991400000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4187</v>
+        <v>-0.4351</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.211399999999999</v>
+        <v>-9.5722</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.53</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4468</v>
+        <v>-0.4615</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.829599999999999</v>
+        <v>-10.153</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.52</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4562</v>
+        <v>-0.4703</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.0364</v>
+        <v>-10.3466</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3692</v>
+        <v>0.3779</v>
       </c>
       <c r="J52" t="n">
-        <v>9.23</v>
+        <v>9.4475</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.042</v>
+        <v>-0.0562</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.05</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1269</v>
+        <v>-0.1442</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.1725</v>
+        <v>-3.605</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.57</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4363</v>
+        <v>-0.4473</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.9075</v>
+        <v>-11.1825</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4363</v>
+        <v>-0.4473</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.9075</v>
+        <v>-11.1825</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8124</v>
+        <v>0.8956</v>
       </c>
       <c r="J57" t="n">
-        <v>20.31</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.31</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6251</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>15.6275</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4423</v>
+        <v>0.4881</v>
       </c>
       <c r="J59" t="n">
-        <v>11.0575</v>
+        <v>12.2025</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2073</v>
+        <v>-0.1985</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.1825</v>
+        <v>-4.9625</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.91</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3645</v>
+        <v>-0.3464</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.112500000000001</v>
+        <v>-8.66</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.12</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3031</v>
+        <v>0.303</v>
       </c>
       <c r="J62" t="n">
-        <v>12.124</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0483</v>
+        <v>0.0509</v>
       </c>
       <c r="J63" t="n">
-        <v>1.932</v>
+        <v>2.036</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1604</v>
+        <v>-0.1752</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.416</v>
+        <v>-7.008</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.171</v>
+        <v>-0.1859</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.84</v>
+        <v>-7.436</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.171</v>
+        <v>-0.1859</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.84</v>
+        <v>-7.436</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3186</v>
+        <v>0.3151</v>
       </c>
       <c r="J67" t="n">
-        <v>12.744</v>
+        <v>12.604</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.229</v>
+        <v>0.2304</v>
       </c>
       <c r="J68" t="n">
-        <v>9.16</v>
+        <v>9.215999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.03</v>
       </c>
       <c r="I69" t="n">
-        <v>0.13</v>
+        <v>0.1354</v>
       </c>
       <c r="J69" t="n">
-        <v>5.2</v>
+        <v>5.416</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.13</v>
+        <v>-0.1354</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.2</v>
+        <v>-5.416</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4884</v>
+        <v>-0.4689</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.536</v>
+        <v>-18.756</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.15</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3581</v>
+        <v>0.368</v>
       </c>
       <c r="J72" t="n">
-        <v>10.0268</v>
+        <v>10.304</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3458</v>
+        <v>0.3493</v>
       </c>
       <c r="J73" t="n">
-        <v>9.682399999999999</v>
+        <v>9.7804</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.86</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1673</v>
+        <v>-0.1831</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.6844</v>
+        <v>-5.1268</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.73</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.297</v>
+        <v>-0.3115</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.722</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3447</v>
+        <v>-0.3578</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.6516</v>
+        <v>-10.0184</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7245</v>
+        <v>0.7912</v>
       </c>
       <c r="J77" t="n">
-        <v>20.286</v>
+        <v>22.1536</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0538</v>
+        <v>0.059</v>
       </c>
       <c r="J78" t="n">
-        <v>1.5064</v>
+        <v>1.652</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2285</v>
+        <v>-0.2301</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.398</v>
+        <v>-6.4428</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.92</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2896</v>
+        <v>-0.2873</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.1088</v>
+        <v>-8.0444</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6978</v>
+        <v>-0.6553</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.5384</v>
+        <v>-18.3484</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6445</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>19.335</v>
+        <v>21.579</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.18</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3701</v>
+        <v>0.3945</v>
       </c>
       <c r="J83" t="n">
-        <v>11.103</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1024</v>
+        <v>-0.1133</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.072</v>
+        <v>-3.399</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.18</v>
+        <v>-0.1929</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.4</v>
+        <v>-5.787</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3481</v>
+        <v>-0.3587</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.443</v>
+        <v>-10.761</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.15</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4447</v>
+        <v>0.4783</v>
       </c>
       <c r="J87" t="n">
-        <v>13.341</v>
+        <v>14.349</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1532</v>
+        <v>0.1514</v>
       </c>
       <c r="J88" t="n">
-        <v>4.596</v>
+        <v>4.542</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3848</v>
+        <v>-0.3795</v>
       </c>
       <c r="J89" t="n">
-        <v>-11.544</v>
+        <v>-11.385</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5464</v>
+        <v>-0.5252</v>
       </c>
       <c r="J90" t="n">
-        <v>-16.392</v>
+        <v>-15.756</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.76</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7013</v>
+        <v>-0.6623</v>
       </c>
       <c r="J91" t="n">
-        <v>-21.039</v>
+        <v>-19.869</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.75</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4769</v>
+        <v>1.4563</v>
       </c>
       <c r="J92" t="n">
-        <v>39.8763</v>
+        <v>39.3201</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.15</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4477</v>
+        <v>0.4407</v>
       </c>
       <c r="J93" t="n">
-        <v>12.0879</v>
+        <v>11.8989</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2887</v>
+        <v>0.294</v>
       </c>
       <c r="J94" t="n">
-        <v>7.7949</v>
+        <v>7.938</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4441</v>
+        <v>-0.4208</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.9907</v>
+        <v>-11.3616</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6333</v>
+        <v>-0.5911</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.0991</v>
+        <v>-15.9597</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.15</v>
       </c>
       <c r="I97" t="n">
-        <v>0.41</v>
+        <v>0.394</v>
       </c>
       <c r="J97" t="n">
-        <v>11.07</v>
+        <v>10.638</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.8765</v>
+        <v>-2.2896</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.89</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.128</v>
+        <v>-0.1451</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.456</v>
+        <v>-3.9177</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.66</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3532</v>
+        <v>-0.3679</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.5364</v>
+        <v>-9.933299999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.53</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4743</v>
+        <v>-0.4831</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.8061</v>
+        <v>-13.0437</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4633</v>
+        <v>0.4612</v>
       </c>
       <c r="J102" t="n">
-        <v>12.9724</v>
+        <v>12.9136</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3143</v>
+        <v>0.3209</v>
       </c>
       <c r="J103" t="n">
-        <v>8.8004</v>
+        <v>8.985200000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.06</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1191</v>
+        <v>0.1299</v>
       </c>
       <c r="J104" t="n">
-        <v>3.3348</v>
+        <v>3.6372</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2326</v>
+        <v>-0.2453</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.5128</v>
+        <v>-6.8684</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.8</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2427</v>
+        <v>-0.2553</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.7956</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.478</v>
+        <v>0.4779</v>
       </c>
       <c r="J107" t="n">
-        <v>13.384</v>
+        <v>13.3812</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2834</v>
+        <v>0.2919</v>
       </c>
       <c r="J108" t="n">
-        <v>7.9352</v>
+        <v>8.1732</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2419</v>
+        <v>0.2514</v>
       </c>
       <c r="J109" t="n">
-        <v>6.7732</v>
+        <v>7.0392</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.6</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4243</v>
+        <v>-0.4333</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.8804</v>
+        <v>-12.1324</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.479</v>
+        <v>-0.4854</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.412</v>
+        <v>-13.5912</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.84</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5491</v>
+        <v>1.5379</v>
       </c>
       <c r="J112" t="n">
-        <v>34.0802</v>
+        <v>33.8338</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6696</v>
+        <v>0.6451</v>
       </c>
       <c r="J113" t="n">
-        <v>14.7312</v>
+        <v>14.1922</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5535</v>
+        <v>0.5407</v>
       </c>
       <c r="J114" t="n">
-        <v>12.177</v>
+        <v>11.8954</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4018</v>
+        <v>0.4035</v>
       </c>
       <c r="J115" t="n">
-        <v>8.839600000000001</v>
+        <v>8.877000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7359</v>
+        <v>-0.6776</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.1898</v>
+        <v>-14.9072</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.41</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>20.4578</v>
+        <v>18.9288</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1327</v>
+        <v>-0.1514</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.9194</v>
+        <v>-3.3308</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3002</v>
+        <v>-0.3177</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.6044</v>
+        <v>-6.9894</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.64</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3664</v>
+        <v>-0.3815</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.0608</v>
+        <v>-8.393000000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.33</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6496</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.3374</v>
+        <v>-14.2912</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7004</v>
+        <v>0.6571</v>
       </c>
       <c r="J122" t="n">
-        <v>21.012</v>
+        <v>19.713</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4628</v>
+        <v>0.4454</v>
       </c>
       <c r="J123" t="n">
-        <v>13.884</v>
+        <v>13.362</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3211</v>
+        <v>0.3161</v>
       </c>
       <c r="J124" t="n">
-        <v>9.632999999999999</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6716</v>
+        <v>-0.6323</v>
       </c>
       <c r="J125" t="n">
-        <v>-20.148</v>
+        <v>-18.969</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7732</v>
+        <v>-0.7216</v>
       </c>
       <c r="J126" t="n">
-        <v>-23.196</v>
+        <v>-21.648</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.62</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>1.0643</v>
       </c>
       <c r="J127" t="n">
-        <v>33</v>
+        <v>31.929</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.14</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3372</v>
+        <v>0.3364</v>
       </c>
       <c r="J128" t="n">
-        <v>10.116</v>
+        <v>10.092</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2838</v>
+        <v>-0.2974</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.513999999999999</v>
+        <v>-8.922000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3128</v>
+        <v>-0.3257</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.384</v>
+        <v>-9.771000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4435</v>
+        <v>-0.4515</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.305</v>
+        <v>-13.545</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9418</v>
+        <v>0.8821</v>
       </c>
       <c r="J132" t="n">
-        <v>22.6032</v>
+        <v>21.1704</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7821</v>
+        <v>0.7408</v>
       </c>
       <c r="J133" t="n">
-        <v>18.7704</v>
+        <v>17.7792</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7114</v>
+        <v>0.6784</v>
       </c>
       <c r="J134" t="n">
-        <v>17.0736</v>
+        <v>16.2816</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0574</v>
+        <v>0.0747</v>
       </c>
       <c r="J135" t="n">
-        <v>1.3776</v>
+        <v>1.7928</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.87</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4783</v>
+        <v>-0.4506</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.4792</v>
+        <v>-10.8144</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5788</v>
+        <v>0.5473</v>
       </c>
       <c r="J137" t="n">
-        <v>13.8912</v>
+        <v>13.1352</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1472</v>
+        <v>-0.1651</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.5328</v>
+        <v>-3.9624</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1682</v>
+        <v>-0.1863</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.0368</v>
+        <v>-4.4712</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.62</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3883</v>
+        <v>-0.4019</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.3192</v>
+        <v>-9.6456</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.51</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4903</v>
+        <v>-0.4986</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.7672</v>
+        <v>-11.9664</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.08</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2538</v>
+        <v>0.2481</v>
       </c>
       <c r="J142" t="n">
-        <v>6.0912</v>
+        <v>5.9544</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0326</v>
+        <v>-0.0448</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.7824</v>
+        <v>-1.0752</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.78</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2403</v>
+        <v>-0.2576</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.7672</v>
+        <v>-6.1824</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2792</v>
+        <v>-0.2957</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.7008</v>
+        <v>-7.0968</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.68</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3365</v>
+        <v>-0.3514</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.076000000000001</v>
+        <v>-8.4336</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.58</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2672</v>
+        <v>1.2343</v>
       </c>
       <c r="J147" t="n">
-        <v>30.4128</v>
+        <v>29.6232</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.37</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9759</v>
+        <v>0.9129</v>
       </c>
       <c r="J148" t="n">
-        <v>23.4216</v>
+        <v>21.9096</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.11</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3472</v>
+        <v>0.3475</v>
       </c>
       <c r="J149" t="n">
-        <v>8.332800000000001</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2931</v>
+        <v>-0.2825</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.0344</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.1213</v>
+        <v>-1.018</v>
       </c>
       <c r="J151" t="n">
-        <v>-26.9112</v>
+        <v>-24.432</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.54</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0048</v>
+        <v>0.955</v>
       </c>
       <c r="J152" t="n">
-        <v>28.1344</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.36</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7211</v>
+        <v>0.6912</v>
       </c>
       <c r="J153" t="n">
-        <v>20.1908</v>
+        <v>19.3536</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.8</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2388</v>
+        <v>-0.2522</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.6864</v>
+        <v>-7.0616</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3736</v>
+        <v>-0.3839</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.4608</v>
+        <v>-10.7492</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.63</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4015</v>
+        <v>-0.4106</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.242</v>
+        <v>-11.4968</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.21</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6801</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>19.0428</v>
+        <v>17.7408</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3146</v>
+        <v>0.3047</v>
       </c>
       <c r="J158" t="n">
-        <v>8.8088</v>
+        <v>8.531599999999999</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3024</v>
+        <v>-0.3032</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.4672</v>
+        <v>-8.489599999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6528</v>
+        <v>-0.6192</v>
       </c>
       <c r="J160" t="n">
-        <v>-18.2784</v>
+        <v>-17.3376</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.7</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8542</v>
+        <v>-0.7953</v>
       </c>
       <c r="J161" t="n">
-        <v>-23.9176</v>
+        <v>-22.2684</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5112</v>
+        <v>0.495</v>
       </c>
       <c r="J162" t="n">
-        <v>14.3136</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0606</v>
+        <v>-0.0743</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.6968</v>
+        <v>-2.0804</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>0.84</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1818</v>
+        <v>-0.1991</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.0904</v>
+        <v>-5.5748</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3088</v>
+        <v>-0.3244</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.6464</v>
+        <v>-9.0832</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5135</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.378</v>
+        <v>-14.5516</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6734</v>
+        <v>0.667</v>
       </c>
       <c r="J167" t="n">
-        <v>18.8552</v>
+        <v>18.676</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.25</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3576</v>
+        <v>0.3696</v>
       </c>
       <c r="J168" t="n">
-        <v>10.0128</v>
+        <v>10.3488</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0722</v>
+        <v>-0.0794</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.0216</v>
+        <v>-2.2232</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.92</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1211</v>
+        <v>-0.131</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.3908</v>
+        <v>-3.668</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2587</v>
+        <v>-0.2699</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.2436</v>
+        <v>-7.5572</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.145</v>
+        <v>1.1024</v>
       </c>
       <c r="J172" t="n">
-        <v>26.335</v>
+        <v>25.3552</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.48</v>
       </c>
       <c r="I173" t="n">
-        <v>1.145</v>
+        <v>1.1024</v>
       </c>
       <c r="J173" t="n">
-        <v>26.335</v>
+        <v>25.3552</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.95</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2226</v>
+        <v>-0.2178</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.1198</v>
+        <v>-5.0094</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6481</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.9063</v>
+        <v>-13.9472</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.6968</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.2615</v>
+        <v>-16.0264</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6216</v>
+        <v>0.5885</v>
       </c>
       <c r="J177" t="n">
-        <v>14.2968</v>
+        <v>13.5355</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.95</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0578</v>
+        <v>-0.0722</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.3294</v>
+        <v>-1.6606</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.82</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1999</v>
+        <v>-0.2178</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.5977</v>
+        <v>-5.0094</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3161</v>
+        <v>-0.3319</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.2703</v>
+        <v>-7.6337</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.47</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5299</v>
+        <v>-0.5353</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.1877</v>
+        <v>-12.3119</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.9</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5781</v>
+        <v>1.5749</v>
       </c>
       <c r="J182" t="n">
-        <v>34.7182</v>
+        <v>34.6478</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.47</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0697</v>
+        <v>1.0315</v>
       </c>
       <c r="J183" t="n">
-        <v>23.5334</v>
+        <v>22.693</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.31</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7815</v>
+        <v>0.7492</v>
       </c>
       <c r="J184" t="n">
-        <v>17.193</v>
+        <v>16.4824</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.31</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7815</v>
+        <v>0.7492</v>
       </c>
       <c r="J185" t="n">
-        <v>17.193</v>
+        <v>16.4824</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.356</v>
+        <v>-0.3267</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.832</v>
+        <v>-7.1874</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>0.97</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0649</v>
+        <v>0.015</v>
       </c>
       <c r="J187" t="n">
-        <v>1.4278</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>0.71</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2748</v>
+        <v>-0.2982</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.0456</v>
+        <v>-6.5604</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.52</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4507</v>
+        <v>-0.466</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.9154</v>
+        <v>-10.252</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4884</v>
+        <v>-0.5012</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.7448</v>
+        <v>-11.0264</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.44</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5262</v>
+        <v>-0.5365</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.5764</v>
+        <v>-11.803</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.46</v>
       </c>
       <c r="I192" t="n">
-        <v>1.132</v>
+        <v>1.086</v>
       </c>
       <c r="J192" t="n">
-        <v>31.696</v>
+        <v>30.408</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.21</v>
       </c>
       <c r="I193" t="n">
-        <v>0.625</v>
+        <v>0.595</v>
       </c>
       <c r="J193" t="n">
-        <v>17.5</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.17</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5221</v>
+        <v>0.5031</v>
       </c>
       <c r="J194" t="n">
-        <v>14.6188</v>
+        <v>14.0868</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.7893</v>
+        <v>-0.7329</v>
       </c>
       <c r="J195" t="n">
-        <v>-22.1004</v>
+        <v>-20.5212</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9373</v>
+        <v>-0.8618</v>
       </c>
       <c r="J196" t="n">
-        <v>-26.2444</v>
+        <v>-24.1304</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4092</v>
+        <v>0.401</v>
       </c>
       <c r="J197" t="n">
-        <v>11.4576</v>
+        <v>11.228</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0533</v>
+        <v>0.0545</v>
       </c>
       <c r="J198" t="n">
-        <v>1.4924</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.137</v>
+        <v>-0.1518</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.836</v>
+        <v>-4.2504</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2198</v>
+        <v>-0.2353</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.1544</v>
+        <v>-6.5884</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2888</v>
+        <v>-0.3032</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.086399999999999</v>
+        <v>-8.489599999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8438</v>
+        <v>0.7839</v>
       </c>
       <c r="J202" t="n">
-        <v>24.4702</v>
+        <v>22.7331</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>1.1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3454</v>
+        <v>0.3396</v>
       </c>
       <c r="J203" t="n">
-        <v>10.0166</v>
+        <v>9.8484</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.98</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1009</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.7753</v>
+        <v>-2.9261</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5184</v>
+        <v>-0.4952</v>
       </c>
       <c r="J205" t="n">
-        <v>-15.0336</v>
+        <v>-14.3608</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.84</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5184</v>
+        <v>-0.4952</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.0336</v>
+        <v>-14.3608</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3658</v>
+        <v>0.3654</v>
       </c>
       <c r="J207" t="n">
-        <v>10.6082</v>
+        <v>10.5966</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2479</v>
+        <v>0.2536</v>
       </c>
       <c r="J208" t="n">
-        <v>7.1891</v>
+        <v>7.3544</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.8183</v>
+        <v>-2.0909</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0985</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.5375</v>
+        <v>-2.8565</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2283</v>
+        <v>-0.2419</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.6207</v>
+        <v>-7.0151</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.11</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3726</v>
+        <v>0.3648</v>
       </c>
       <c r="J212" t="n">
-        <v>10.0602</v>
+        <v>9.849600000000001</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.02</v>
       </c>
       <c r="I213" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J213" t="n">
-        <v>2.4516</v>
+        <v>2.6352</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0514</v>
+        <v>0.0574</v>
       </c>
       <c r="J214" t="n">
-        <v>1.3878</v>
+        <v>1.5498</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1333</v>
+        <v>-0.1377</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.5991</v>
+        <v>-3.7179</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1679</v>
+        <v>-0.1712</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.5333</v>
+        <v>-4.6224</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.13</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3233</v>
+        <v>0.322</v>
       </c>
       <c r="J217" t="n">
-        <v>8.729100000000001</v>
+        <v>8.694000000000001</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.02</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0775</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>2.0925</v>
+        <v>2.2032</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.95</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.9278</v>
+        <v>-2.2302</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0946</v>
+        <v>-0.1073</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.5542</v>
+        <v>-2.8971</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3392</v>
+        <v>-0.3517</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.1584</v>
+        <v>-9.495900000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.39</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0177</v>
+        <v>0.9566</v>
       </c>
       <c r="J222" t="n">
-        <v>22.3894</v>
+        <v>21.0452</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.38</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0007</v>
+        <v>0.9377</v>
       </c>
       <c r="J223" t="n">
-        <v>22.0154</v>
+        <v>20.6294</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7785</v>
+        <v>0.7339</v>
       </c>
       <c r="J224" t="n">
-        <v>17.127</v>
+        <v>16.1458</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.676</v>
       </c>
       <c r="J225" t="n">
-        <v>-16.0006</v>
+        <v>-14.872</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.8498</v>
       </c>
       <c r="J226" t="n">
-        <v>-20.3698</v>
+        <v>-18.6956</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5567</v>
+        <v>0.5309</v>
       </c>
       <c r="J227" t="n">
-        <v>12.2474</v>
+        <v>11.6798</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.162</v>
+        <v>-0.1791</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.564</v>
+        <v>-3.9402</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2113</v>
+        <v>-0.2288</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.6486</v>
+        <v>-5.0336</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2113</v>
+        <v>-0.2288</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.6486</v>
+        <v>-5.0336</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4492</v>
+        <v>-0.459</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.882400000000001</v>
+        <v>-10.098</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>2.01</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7161</v>
+        <v>1.7171</v>
       </c>
       <c r="J232" t="n">
-        <v>36.0381</v>
+        <v>36.0591</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.44</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0369</v>
+        <v>0.9911</v>
       </c>
       <c r="J233" t="n">
-        <v>21.7749</v>
+        <v>20.8131</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.34</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8536</v>
+        <v>0.8115</v>
       </c>
       <c r="J234" t="n">
-        <v>17.9256</v>
+        <v>17.0415</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.07</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1814</v>
+        <v>0.2053</v>
       </c>
       <c r="J235" t="n">
-        <v>3.8094</v>
+        <v>4.3113</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5298</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.0771</v>
+        <v>-11.1258</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>0.86</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1199</v>
+        <v>-0.1462</v>
       </c>
       <c r="J237" t="n">
-        <v>-2.5179</v>
+        <v>-3.0702</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>0.78</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2091</v>
+        <v>-0.2335</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.3911</v>
+        <v>-4.9035</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3275</v>
+        <v>-0.348</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.8775</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.5</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4742</v>
+        <v>-0.4873</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.9582</v>
+        <v>-10.2333</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5214</v>
+        <v>-0.5313</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.9494</v>
+        <v>-11.1573</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8235</v>
+        <v>0.7696</v>
       </c>
       <c r="J242" t="n">
-        <v>27.999</v>
+        <v>26.1664</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7746</v>
+        <v>0.7269</v>
       </c>
       <c r="J243" t="n">
-        <v>26.3364</v>
+        <v>24.7146</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0931</v>
       </c>
       <c r="J244" t="n">
-        <v>2.8594</v>
+        <v>3.1654</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.86</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4764</v>
+        <v>-0.4549</v>
       </c>
       <c r="J245" t="n">
-        <v>-16.1976</v>
+        <v>-15.4666</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.584</v>
+        <v>-0.5515</v>
       </c>
       <c r="J246" t="n">
-        <v>-19.856</v>
+        <v>-18.751</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.22</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5204</v>
+        <v>0.5007</v>
       </c>
       <c r="J247" t="n">
-        <v>17.6936</v>
+        <v>17.0238</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2163</v>
+        <v>0.2154</v>
       </c>
       <c r="J248" t="n">
-        <v>7.3542</v>
+        <v>7.3236</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.99</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0158</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.2788</v>
+        <v>-0.5372</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.67</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3511</v>
+        <v>-0.3645</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.9374</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.49</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5172</v>
+        <v>-0.5225</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.5848</v>
+        <v>-17.765</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.5</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1802</v>
+        <v>1.1385</v>
       </c>
       <c r="J252" t="n">
-        <v>33.0456</v>
+        <v>31.878</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1835</v>
+        <v>0.191</v>
       </c>
       <c r="J253" t="n">
-        <v>5.138</v>
+        <v>5.348</v>
       </c>
     </row>
     <row r="254">
@@ -12595,10 +12595,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3391</v>
+        <v>-0.3286</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.4948</v>
+        <v>-9.200799999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3391</v>
+        <v>-0.3286</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.4948</v>
+        <v>-9.200799999999999</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0398</v>
+        <v>0.0288</v>
       </c>
       <c r="J257" t="n">
-        <v>1.1144</v>
+        <v>0.8064</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.95</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0582</v>
+        <v>-0.0725</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.6296</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.8</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2197</v>
+        <v>-0.2375</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.1516</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.75</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2684</v>
+        <v>-0.2854</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.5152</v>
+        <v>-7.9912</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.71</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3069</v>
+        <v>-0.3229</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.5932</v>
+        <v>-9.0412</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.89</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5994</v>
+        <v>1.592</v>
       </c>
       <c r="J262" t="n">
-        <v>35.1868</v>
+        <v>35.024</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.63</v>
       </c>
       <c r="I263" t="n">
-        <v>1.287</v>
+        <v>1.2629</v>
       </c>
       <c r="J263" t="n">
-        <v>28.314</v>
+        <v>27.7838</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4984</v>
+        <v>0.4924</v>
       </c>
       <c r="J264" t="n">
-        <v>10.9648</v>
+        <v>10.8328</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2997</v>
+        <v>-0.2797</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.5934</v>
+        <v>-6.1534</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.71</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.9151</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-20.1322</v>
+        <v>-18.3524</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0366</v>
+        <v>-0.0556</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.8052</v>
+        <v>-1.2232</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1452</v>
+        <v>-0.1661</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.1944</v>
+        <v>-3.6542</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2569</v>
+        <v>-0.2766</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.6518</v>
+        <v>-6.0852</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.415</v>
+        <v>-0.4291</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.130000000000001</v>
+        <v>-9.440200000000001</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.415</v>
+        <v>-0.4291</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.130000000000001</v>
+        <v>-9.440200000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>2.03</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7488</v>
+        <v>1.7496</v>
       </c>
       <c r="J272" t="n">
-        <v>34.976</v>
+        <v>34.992</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.75</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4213</v>
+        <v>1.407</v>
       </c>
       <c r="J273" t="n">
-        <v>28.426</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.07</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1883</v>
+        <v>0.2101</v>
       </c>
       <c r="J274" t="n">
-        <v>3.766</v>
+        <v>4.202</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5143</v>
+        <v>-0.476</v>
       </c>
       <c r="J275" t="n">
-        <v>-10.286</v>
+        <v>-9.52</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5956</v>
+        <v>-0.5494</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.912</v>
+        <v>-10.988</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1286</v>
+        <v>0.1097</v>
       </c>
       <c r="J277" t="n">
-        <v>2.572</v>
+        <v>2.194</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.96</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0211</v>
+        <v>-0.0398</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.422</v>
+        <v>-0.796</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.6</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3954</v>
+        <v>-0.4106</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.908</v>
+        <v>-8.212</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4328</v>
+        <v>-0.446</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.656000000000001</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4328</v>
+        <v>-0.446</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.656000000000001</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.48</v>
       </c>
       <c r="I282" t="n">
-        <v>1.1187</v>
+        <v>1.0791</v>
       </c>
       <c r="J282" t="n">
-        <v>29.0862</v>
+        <v>28.0566</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>1.36</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9327</v>
+        <v>0.8752</v>
       </c>
       <c r="J283" t="n">
-        <v>24.2502</v>
+        <v>22.7552</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7553</v>
       </c>
       <c r="J284" t="n">
-        <v>20.7194</v>
+        <v>19.6378</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>1.03</v>
       </c>
       <c r="I285" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1062</v>
       </c>
       <c r="J285" t="n">
-        <v>2.275</v>
+        <v>2.7612</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7488</v>
+        <v>-0.6912</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.4688</v>
+        <v>-17.9712</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>0.0622</v>
+        <v>0.0452</v>
       </c>
       <c r="J287" t="n">
-        <v>1.6172</v>
+        <v>1.1752</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0474</v>
+        <v>-0.0641</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.2324</v>
+        <v>-1.6666</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.195</v>
+        <v>-0.214</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.07</v>
+        <v>-5.564</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.224</v>
+        <v>-0.2429</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.824</v>
+        <v>-6.3154</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.38</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6057</v>
+        <v>-0.607</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.7482</v>
+        <v>-15.782</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.12</v>
       </c>
       <c r="I292" t="n">
-        <v>0.282</v>
+        <v>0.2876</v>
       </c>
       <c r="J292" t="n">
-        <v>8.460000000000001</v>
+        <v>8.628</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2622</v>
+        <v>0.2687</v>
       </c>
       <c r="J293" t="n">
-        <v>7.866</v>
+        <v>8.061</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="J294" t="n">
-        <v>1.911</v>
+        <v>2.151</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.09</v>
+        <v>-0.1005</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.7</v>
+        <v>-3.015</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.9</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1362</v>
+        <v>-0.1485</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.086</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.15</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4986</v>
+        <v>0.476</v>
       </c>
       <c r="J297" t="n">
-        <v>14.958</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.11</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3867</v>
+        <v>0.3746</v>
       </c>
       <c r="J298" t="n">
-        <v>11.601</v>
+        <v>11.238</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.04</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1713</v>
+        <v>0.1736</v>
       </c>
       <c r="J299" t="n">
-        <v>5.139</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>0.88</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3987</v>
+        <v>-0.3891</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.961</v>
+        <v>-11.673</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.7</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8667</v>
+        <v>-0.8041</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.001</v>
+        <v>-24.123</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>0.99</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0219</v>
+        <v>-0</v>
       </c>
       <c r="J302" t="n">
-        <v>0.4599</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0853</v>
+        <v>-0.1034</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.7913</v>
+        <v>-2.1714</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1849</v>
+        <v>-0.204</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.8829</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.68</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3278</v>
+        <v>-0.3445</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.8838</v>
+        <v>-7.2345</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4773</v>
+        <v>-0.4869</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.0233</v>
+        <v>-10.2249</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.34</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8868</v>
+        <v>0.8343</v>
       </c>
       <c r="J307" t="n">
-        <v>18.6228</v>
+        <v>17.5203</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.26</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7023</v>
+        <v>0.6721</v>
       </c>
       <c r="J308" t="n">
-        <v>14.7483</v>
+        <v>14.1141</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.6081</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J309" t="n">
-        <v>12.7701</v>
+        <v>12.3522</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.17</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4888</v>
+        <v>0.4803</v>
       </c>
       <c r="J310" t="n">
-        <v>10.2648</v>
+        <v>10.0863</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.98</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1432</v>
+        <v>-0.1338</v>
       </c>
       <c r="J311" t="n">
-        <v>-3.0072</v>
+        <v>-2.8098</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1986/event_1986_evp_summary.xlsx
+++ b/database/event/1986/event_1986_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6558</v>
+        <v>6.4863</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9653</v>
+        <v>3.8643</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4057</v>
+        <v>2.349</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6558</v>
+        <v>6.4863</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5807</v>
+        <v>4.605</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0751</v>
+        <v>1.8813</v>
       </c>
       <c r="H2" t="n">
-        <v>12.4233</v>
+        <v>11.9325</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7085</v>
+        <v>6.6997</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0751</v>
+        <v>1.8813</v>
       </c>
       <c r="K2" t="n">
         <v>189</v>
@@ -529,7 +529,7 @@
         <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>8.7836</v>
+        <v>8.581</v>
       </c>
       <c r="N2" t="n">
         <v>388</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7619</v>
+        <v>5.6097</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4328</v>
+        <v>3.3421</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9987</v>
+        <v>1.9497</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7619</v>
+        <v>5.6097</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6439</v>
+        <v>3.4954</v>
       </c>
       <c r="G3" t="n">
-        <v>2.118</v>
+        <v>2.1143</v>
       </c>
       <c r="H3" t="n">
-        <v>7.1283</v>
+        <v>6.6805</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8492</v>
+        <v>3.7509</v>
       </c>
       <c r="J3" t="n">
-        <v>2.118</v>
+        <v>2.1143</v>
       </c>
       <c r="K3" t="n">
         <v>149</v>
@@ -575,7 +575,7 @@
         <v>192</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9672</v>
+        <v>5.8652</v>
       </c>
       <c r="N3" t="n">
         <v>341</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4349</v>
+        <v>4.3448</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6422</v>
+        <v>2.5885</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3947</v>
+        <v>1.3735</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4349</v>
+        <v>4.3448</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3476</v>
+        <v>3.3449</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0873</v>
+        <v>0.9999</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1507</v>
+        <v>6.1154</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3213</v>
+        <v>3.4336</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0873</v>
+        <v>0.9999</v>
       </c>
       <c r="K4" t="n">
         <v>107</v>
@@ -621,7 +621,7 @@
         <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4086</v>
+        <v>4.4335</v>
       </c>
       <c r="N4" t="n">
         <v>165</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4321</v>
+        <v>3.2463</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0447</v>
+        <v>1.9341</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9382</v>
+        <v>0.8731</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4321</v>
+        <v>3.2463</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1349</v>
+        <v>3.0373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2972</v>
+        <v>0.209</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4492</v>
+        <v>4.9607</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9425</v>
+        <v>2.7853</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2972</v>
+        <v>0.209</v>
       </c>
       <c r="K5" t="n">
         <v>189</v>
@@ -667,7 +667,7 @@
         <v>199</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2397</v>
+        <v>2.9943</v>
       </c>
       <c r="N5" t="n">
         <v>388</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6134</v>
+        <v>2.5494</v>
       </c>
       <c r="C6" t="n">
-        <v>1.557</v>
+        <v>1.5189</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5655</v>
+        <v>0.5556</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6134</v>
+        <v>2.5494</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6189</v>
+        <v>2.5494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9945000000000001</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6189</v>
+        <v>2.8923</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8742</v>
+        <v>2.8923</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9945000000000001</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="L6" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8687</v>
+        <v>2.8923</v>
       </c>
       <c r="N6" t="n">
-        <v>388</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6037</v>
+        <v>2.4186</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5512</v>
+        <v>1.4409</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5611</v>
+        <v>0.496</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6037</v>
+        <v>2.4186</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6037</v>
+        <v>1.5383</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.8803</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9737</v>
+        <v>1.5383</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9737</v>
+        <v>0.8637</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.8803</v>
       </c>
       <c r="K7" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9737</v>
+        <v>1.744</v>
       </c>
       <c r="N7" t="n">
-        <v>178</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4032</v>
+        <v>2.3835</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4318</v>
+        <v>1.42</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4698</v>
+        <v>0.48</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4032</v>
+        <v>2.3835</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0734</v>
+        <v>3.0225</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6702</v>
+        <v>-0.639</v>
       </c>
       <c r="H8" t="n">
-        <v>5.246</v>
+        <v>4.905</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8328</v>
+        <v>2.754</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6702</v>
+        <v>-0.639</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -805,7 +805,7 @@
         <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1626</v>
+        <v>2.115</v>
       </c>
       <c r="N8" t="n">
         <v>165</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3124</v>
+        <v>2.3594</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3777</v>
+        <v>1.4057</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4284</v>
+        <v>0.469</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3124</v>
+        <v>2.3594</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3124</v>
+        <v>2.5602</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.2008</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3362</v>
+        <v>3.1695</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3362</v>
+        <v>1.7796</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.2008</v>
       </c>
       <c r="K9" t="n">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3362</v>
+        <v>1.5788</v>
       </c>
       <c r="N9" t="n">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2803</v>
+        <v>2.1544</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3585</v>
+        <v>1.2835</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4138</v>
+        <v>0.3756</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2803</v>
+        <v>2.1544</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5117</v>
+        <v>2.1544</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2314</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3928</v>
+        <v>2.1544</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8321</v>
+        <v>2.1544</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2314</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="L10" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6007</v>
+        <v>2.1544</v>
       </c>
       <c r="N10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1184</v>
+        <v>2.1459</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2621</v>
+        <v>1.2785</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3401</v>
+        <v>0.3718</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1184</v>
+        <v>2.1459</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1184</v>
+        <v>2.1459</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1184</v>
+        <v>2.1459</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1184</v>
+        <v>2.1459</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1184</v>
+        <v>2.1459</v>
       </c>
       <c r="N11" t="n">
         <v>178</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.038</v>
+        <v>2.0922</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2142</v>
+        <v>1.2465</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3035</v>
+        <v>0.3473</v>
       </c>
       <c r="E12" t="n">
-        <v>2.038</v>
+        <v>2.0922</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1823</v>
+        <v>2.2804</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1443</v>
+        <v>-0.1882</v>
       </c>
       <c r="H12" t="n">
-        <v>2.306</v>
+        <v>2.2804</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2452</v>
+        <v>1.2804</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1443</v>
+        <v>-0.1882</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>65</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1009</v>
+        <v>1.0922</v>
       </c>
       <c r="N12" t="n">
         <v>165</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9679</v>
+        <v>1.7502</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1724</v>
+        <v>1.0427</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2716</v>
+        <v>0.1915</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9679</v>
+        <v>1.7502</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5391</v>
+        <v>1.3878</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4288</v>
+        <v>0.3624</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5391</v>
+        <v>1.3878</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.7792</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4288</v>
+        <v>0.3624</v>
       </c>
       <c r="K13" t="n">
         <v>100</v>
@@ -1035,7 +1035,7 @@
         <v>65</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2599</v>
+        <v>1.1416</v>
       </c>
       <c r="N13" t="n">
         <v>165</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1202</v>
+        <v>1.2163</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6674</v>
+        <v>0.7246</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1143</v>
+        <v>-0.0517</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1202</v>
+        <v>1.2163</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7104</v>
+        <v>2.7337</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5902</v>
+        <v>-1.5174</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0486</v>
+        <v>3.8209</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1862</v>
+        <v>2.1453</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5902</v>
+        <v>-1.5174</v>
       </c>
       <c r="K14" t="n">
         <v>149</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5959999999999999</v>
+        <v>0.6279000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>341</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6472</v>
+        <v>0.6</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3856</v>
+        <v>0.3575</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3296</v>
+        <v>-0.3325</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6472</v>
+        <v>0.6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6472</v>
+        <v>0.6</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6472</v>
+        <v>0.6</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6472</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6472</v>
+        <v>0.6</v>
       </c>
       <c r="N15" t="n">
         <v>184</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.554</v>
+        <v>0.527</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3301</v>
+        <v>0.314</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.372</v>
+        <v>-0.3657</v>
       </c>
       <c r="E16" t="n">
-        <v>0.554</v>
+        <v>0.527</v>
       </c>
       <c r="F16" t="n">
-        <v>0.318</v>
+        <v>0.3258</v>
       </c>
       <c r="G16" t="n">
-        <v>0.236</v>
+        <v>0.2012</v>
       </c>
       <c r="H16" t="n">
-        <v>0.318</v>
+        <v>0.3258</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1717</v>
+        <v>0.1829</v>
       </c>
       <c r="J16" t="n">
-        <v>0.236</v>
+        <v>0.2012</v>
       </c>
       <c r="K16" t="n">
         <v>107</v>
@@ -1173,7 +1173,7 @@
         <v>58</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4077</v>
+        <v>0.3841</v>
       </c>
       <c r="N16" t="n">
         <v>165</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.539</v>
+        <v>0.4357</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3211</v>
+        <v>0.2596</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3788</v>
+        <v>-0.4073</v>
       </c>
       <c r="E17" t="n">
-        <v>0.539</v>
+        <v>0.4357</v>
       </c>
       <c r="F17" t="n">
-        <v>0.539</v>
+        <v>0.4357</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.539</v>
+        <v>0.4357</v>
       </c>
       <c r="I17" t="n">
-        <v>0.539</v>
+        <v>0.4357</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.539</v>
+        <v>0.4357</v>
       </c>
       <c r="N17" t="n">
         <v>102</v>
@@ -1228,185 +1228,185 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mOE</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2687</v>
+        <v>0.2556</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1601</v>
+        <v>0.1523</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5019</v>
+        <v>-0.4893</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2687</v>
+        <v>0.2556</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2687</v>
+        <v>0.2556</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2687</v>
+        <v>0.2556</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2687</v>
+        <v>0.2556</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2687</v>
+        <v>0.2556</v>
       </c>
       <c r="N18" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>mOE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2664</v>
+        <v>0.2274</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1587</v>
+        <v>0.1355</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5029</v>
+        <v>-0.5022</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2664</v>
+        <v>0.2274</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8996</v>
+        <v>0.2274</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6332</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8996</v>
+        <v>0.2274</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4858</v>
+        <v>0.2274</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6332</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="L19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1474</v>
+        <v>0.2274</v>
       </c>
       <c r="N19" t="n">
-        <v>165</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2545</v>
+        <v>0.2001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1516</v>
+        <v>0.1192</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5083</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2545</v>
+        <v>0.2001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2545</v>
+        <v>0.7117</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2545</v>
+        <v>0.7117</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2545</v>
+        <v>0.3996</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2545</v>
+        <v>-0.112</v>
       </c>
       <c r="N20" t="n">
-        <v>102</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0888</v>
+        <v>0.1426</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0529</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5838</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0888</v>
+        <v>0.1426</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5798</v>
+        <v>0.7488</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.491</v>
+        <v>-0.6062</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5798</v>
+        <v>0.7488</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3131</v>
+        <v>0.4204</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.491</v>
+        <v>-0.6062</v>
       </c>
       <c r="K21" t="n">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="L21" t="n">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1779</v>
+        <v>-0.1858</v>
       </c>
       <c r="N21" t="n">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0798</v>
+        <v>0.1077</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0475</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5879</v>
+        <v>-0.5567</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0798</v>
+        <v>0.1077</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0798</v>
+        <v>0.1077</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0798</v>
+        <v>0.1077</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0798</v>
+        <v>0.1077</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0798</v>
+        <v>0.1077</v>
       </c>
       <c r="N22" t="n">
         <v>119</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1041</v>
+        <v>-0.0027</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.062</v>
+        <v>-0.0016</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6716</v>
+        <v>-0.607</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1041</v>
+        <v>-0.0027</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1041</v>
+        <v>-0.0027</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1041</v>
+        <v>-0.0027</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1041</v>
+        <v>-0.0027</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1041</v>
+        <v>-0.0027</v>
       </c>
       <c r="N23" t="n">
         <v>127</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1177</v>
+        <v>-0.1035</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0701</v>
+        <v>-0.0617</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6778</v>
+        <v>-0.6529</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1177</v>
+        <v>-0.1035</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1177</v>
+        <v>-0.1035</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1177</v>
+        <v>-0.1035</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1177</v>
+        <v>-0.1035</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1177</v>
+        <v>-0.1035</v>
       </c>
       <c r="N24" t="n">
         <v>184</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2712</v>
+        <v>-0.2318</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1616</v>
+        <v>-0.1381</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7477</v>
+        <v>-0.7114</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2712</v>
+        <v>-0.2318</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7383</v>
+        <v>-0.7379</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4671</v>
+        <v>0.5061</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7383</v>
+        <v>-0.7379</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3987</v>
+        <v>-0.4143</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4671</v>
+        <v>0.5061</v>
       </c>
       <c r="K25" t="n">
         <v>149</v>
@@ -1587,7 +1587,7 @@
         <v>192</v>
       </c>
       <c r="M25" t="n">
-        <v>0.06840000000000002</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>341</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5283</v>
+        <v>-0.4005</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3147</v>
+        <v>-0.2386</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8647</v>
+        <v>-0.7882</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5283</v>
+        <v>-0.4005</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3641</v>
+        <v>-0.2841</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1642</v>
+        <v>-0.1164</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3641</v>
+        <v>-0.2841</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1966</v>
+        <v>-0.1595</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1642</v>
+        <v>-0.1164</v>
       </c>
       <c r="K26" t="n">
         <v>149</v>
@@ -1633,7 +1633,7 @@
         <v>192</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3608</v>
+        <v>-0.2759</v>
       </c>
       <c r="N26" t="n">
         <v>341</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5974</v>
+        <v>-0.5909</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3559</v>
+        <v>-0.352</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8962</v>
+        <v>-0.875</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5974</v>
+        <v>-0.5909</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5974</v>
+        <v>-0.5909</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5974</v>
+        <v>-0.5909</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5974</v>
+        <v>-0.5909</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5974</v>
+        <v>-0.5909</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3781</v>
+        <v>-0.3766</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9131</v>
+        <v>-0.8938</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6322</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.7006</v>
+        <v>-0.6372</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4174</v>
+        <v>-0.3796</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9431</v>
+        <v>-0.8961</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7006</v>
+        <v>-0.6372</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7006</v>
+        <v>-0.6372</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7006</v>
+        <v>-0.6372</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7006</v>
+        <v>-0.6372</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.7006</v>
+        <v>-0.6372</v>
       </c>
       <c r="N29" t="n">
         <v>102</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.004</v>
+        <v>-1.0167</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5982</v>
+        <v>-0.6057</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0812</v>
+        <v>-1.0689</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.004</v>
+        <v>-1.0167</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.004</v>
+        <v>-1.0167</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.004</v>
+        <v>-1.0167</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.004</v>
+        <v>-1.0167</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.004</v>
+        <v>-1.0167</v>
       </c>
       <c r="N30" t="n">
         <v>184</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0848</v>
+        <v>-1.0283</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6463</v>
+        <v>-0.6126</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.118</v>
+        <v>-1.0742</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0848</v>
+        <v>-1.0283</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0848</v>
+        <v>-1.0283</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0848</v>
+        <v>-1.0283</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0848</v>
+        <v>-1.0283</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0848</v>
+        <v>-1.0283</v>
       </c>
       <c r="N31" t="n">
         <v>102</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.1719</v>
+        <v>-1.0776</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.6982</v>
+        <v>-0.642</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.1577</v>
+        <v>-1.0967</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.1719</v>
+        <v>-1.0776</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1719</v>
+        <v>-1.0776</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1719</v>
+        <v>-1.0776</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.1719</v>
+        <v>-1.0776</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.1719</v>
+        <v>-1.0776</v>
       </c>
       <c r="N32" t="n">
         <v>178</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.2779</v>
+        <v>-1.2394</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.7613</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.2059</v>
+        <v>-1.1704</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.2779</v>
+        <v>-1.2394</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.2779</v>
+        <v>-1.2394</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.2779</v>
+        <v>-1.2394</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.2779</v>
+        <v>-1.2394</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.2779</v>
+        <v>-1.2394</v>
       </c>
       <c r="N33" t="n">
         <v>119</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.356</v>
+        <v>-1.2983</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.8079</v>
+        <v>-0.7735</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.2415</v>
+        <v>-1.1972</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.356</v>
+        <v>-1.2983</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.356</v>
+        <v>-1.2983</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.356</v>
+        <v>-1.2983</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.356</v>
+        <v>-1.2983</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.356</v>
+        <v>-1.2983</v>
       </c>
       <c r="N34" t="n">
         <v>102</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3837</v>
+        <v>-1.3123</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.8244</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.2541</v>
+        <v>-1.2036</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3837</v>
+        <v>-1.3123</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3837</v>
+        <v>-1.3123</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3837</v>
+        <v>-1.3123</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3837</v>
+        <v>-1.3123</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3837</v>
+        <v>-1.3123</v>
       </c>
       <c r="N35" t="n">
         <v>178</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6317</v>
+        <v>-1.6925</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.9721</v>
+        <v>-1.0083</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.367</v>
+        <v>-1.3768</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6317</v>
+        <v>-1.6925</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6317</v>
+        <v>-1.6925</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.6317</v>
+        <v>-1.6925</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6317</v>
+        <v>-1.6925</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6317</v>
+        <v>-1.6925</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.8279</v>
+        <v>-1.794</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.089</v>
+        <v>-1.0688</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.4563</v>
+        <v>-1.423</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.8279</v>
+        <v>-1.794</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4978</v>
+        <v>-1.5</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3301</v>
+        <v>-0.294</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4978</v>
+        <v>-1.5</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8088</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3301</v>
+        <v>-0.294</v>
       </c>
       <c r="K37" t="n">
         <v>100</v>
@@ -2139,7 +2139,7 @@
         <v>65</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1389</v>
+        <v>-1.1362</v>
       </c>
       <c r="N37" t="n">
         <v>165</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.0353</v>
+        <v>-1.8581</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.2126</v>
+        <v>-1.107</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.5507</v>
+        <v>-1.4522</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.0353</v>
+        <v>-1.8581</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4843</v>
+        <v>-1.2784</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.551</v>
+        <v>-0.5797</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4843</v>
+        <v>-1.2784</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8015</v>
+        <v>-0.7178</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.551</v>
+        <v>-0.5797</v>
       </c>
       <c r="K38" t="n">
         <v>189</v>
@@ -2185,7 +2185,7 @@
         <v>199</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3525</v>
+        <v>-1.2975</v>
       </c>
       <c r="N38" t="n">
         <v>388</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.2308</v>
+        <v>-1.9997</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.329</v>
+        <v>-1.1914</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.6397</v>
+        <v>-1.5167</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2308</v>
+        <v>-1.9997</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.8548</v>
+        <v>-1.664</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.376</v>
+        <v>-0.3357</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.8548</v>
+        <v>-1.664</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0016</v>
+        <v>-0.9343</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.376</v>
+        <v>-0.3357</v>
       </c>
       <c r="K39" t="n">
         <v>107</v>
@@ -2231,7 +2231,7 @@
         <v>58</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3776</v>
+        <v>-1.27</v>
       </c>
       <c r="N39" t="n">
         <v>165</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.5639</v>
+        <v>-3.3121</v>
       </c>
       <c r="C40" t="n">
-        <v>-2.1233</v>
+        <v>-1.9733</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.2466</v>
+        <v>-2.1146</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.5639</v>
+        <v>-3.3121</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.6006</v>
+        <v>-3.3074</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0367</v>
+        <v>-0.0047</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.6006</v>
+        <v>-3.3074</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9443</v>
+        <v>-1.857</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0367</v>
+        <v>-0.0047</v>
       </c>
       <c r="K40" t="n">
         <v>107</v>
@@ -2277,7 +2277,7 @@
         <v>58</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9076</v>
+        <v>-1.8617</v>
       </c>
       <c r="N40" t="n">
         <v>165</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8133</v>
+        <v>-3.7885</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.2719</v>
+        <v>-2.2571</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3601</v>
+        <v>-2.3316</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8133</v>
+        <v>-3.7885</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.8133</v>
+        <v>-3.7885</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.8133</v>
+        <v>-3.7885</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.8133</v>
+        <v>-3.7885</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.8133</v>
+        <v>-3.7885</v>
       </c>
       <c r="N41" t="n">
         <v>184</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-4.3901</v>
+        <v>-4.076</v>
       </c>
       <c r="C42" t="n">
-        <v>-2.6155</v>
+        <v>-2.4284</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.6227</v>
+        <v>-2.4626</v>
       </c>
       <c r="E42" t="n">
-        <v>-4.3901</v>
+        <v>-4.076</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.5806</v>
+        <v>-3.2611</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.8095</v>
+        <v>-0.8149</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.5806</v>
+        <v>-3.2611</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.9335</v>
+        <v>-1.831</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8095</v>
+        <v>-0.8149</v>
       </c>
       <c r="K42" t="n">
         <v>189</v>
@@ -2369,7 +2369,7 @@
         <v>199</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.743</v>
+        <v>-2.6459</v>
       </c>
       <c r="N42" t="n">
         <v>388</v>
@@ -2475,10 +2475,10 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8712</v>
+        <v>0.8524</v>
       </c>
       <c r="J2" t="n">
-        <v>26.136</v>
+        <v>25.572</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3672</v>
+        <v>0.3249</v>
       </c>
       <c r="J3" t="n">
-        <v>11.016</v>
+        <v>9.747</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0587</v>
+        <v>-1.0625</v>
       </c>
       <c r="J6" t="n">
-        <v>-31.761</v>
+        <v>-31.875</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.884</v>
+        <v>0.8411</v>
       </c>
       <c r="J7" t="n">
-        <v>26.52</v>
+        <v>25.233</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2796</v>
+        <v>0.2304</v>
       </c>
       <c r="J8" t="n">
-        <v>8.388</v>
+        <v>6.912</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>0.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1549</v>
+        <v>-0.1354</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.647</v>
+        <v>-4.062</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2084</v>
+        <v>-0.188</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.252</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>0.49</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5286</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.858</v>
+        <v>-16.014</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.38</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9828</v>
+        <v>0.9776</v>
       </c>
       <c r="J12" t="n">
-        <v>29.484</v>
+        <v>29.328</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.291</v>
+        <v>0.2505</v>
       </c>
       <c r="J13" t="n">
-        <v>8.73</v>
+        <v>7.515</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0755</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.928</v>
+        <v>-2.265</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3124</v>
+        <v>-0.2718</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.372</v>
+        <v>-8.154</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.58</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0553</v>
+        <v>-1.0582</v>
       </c>
       <c r="J16" t="n">
-        <v>-31.659</v>
+        <v>-31.746</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3577</v>
+        <v>0.3036</v>
       </c>
       <c r="J17" t="n">
-        <v>10.731</v>
+        <v>9.108000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0222</v>
+        <v>-0.0165</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.666</v>
+        <v>-0.495</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0955</v>
+        <v>-0.0799</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.865</v>
+        <v>-2.397</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1197</v>
+        <v>-0.1022</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.591</v>
+        <v>-3.066</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>0.75</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2963</v>
+        <v>-0.278</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.888999999999999</v>
+        <v>-8.34</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.11</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2562</v>
+        <v>0.247</v>
       </c>
       <c r="J22" t="n">
-        <v>5.6364</v>
+        <v>5.434</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>0.98</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0214</v>
+        <v>-0.014</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4708</v>
+        <v>-0.308</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2155</v>
+        <v>-0.1982</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.741</v>
+        <v>-4.3604</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>0.67</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3554</v>
+        <v>-0.3407</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.8188</v>
+        <v>-7.4954</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>0.44</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5575</v>
+        <v>-0.5649</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.265</v>
+        <v>-12.4278</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5219</v>
+        <v>0.453</v>
       </c>
       <c r="J27" t="n">
-        <v>11.4818</v>
+        <v>9.965999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>1.24</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3457</v>
+        <v>0.2884</v>
       </c>
       <c r="J28" t="n">
-        <v>7.6054</v>
+        <v>6.3448</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2634</v>
+        <v>0.2149</v>
       </c>
       <c r="J29" t="n">
-        <v>5.7948</v>
+        <v>4.7278</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>1.11</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1847</v>
+        <v>0.1463</v>
       </c>
       <c r="J30" t="n">
-        <v>4.0634</v>
+        <v>3.2186</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>1.06</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1099</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>2.4178</v>
+        <v>1.8282</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.07</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1617</v>
+        <v>0.1444</v>
       </c>
       <c r="J32" t="n">
-        <v>4.851</v>
+        <v>4.332</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>0.97</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0533</v>
+        <v>-0.0429</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.599</v>
+        <v>-1.287</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1064</v>
+        <v>-0.0905</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.192</v>
+        <v>-2.715</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1407</v>
+        <v>-0.1226</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.221</v>
+        <v>-3.678</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2938</v>
+        <v>-0.2754</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.814</v>
+        <v>-8.262</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.31</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4519</v>
+        <v>0.386</v>
       </c>
       <c r="J37" t="n">
-        <v>13.557</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.16</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2678</v>
+        <v>0.2152</v>
       </c>
       <c r="J38" t="n">
-        <v>8.034000000000001</v>
+        <v>6.456</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2411</v>
+        <v>0.1915</v>
       </c>
       <c r="J39" t="n">
-        <v>7.233</v>
+        <v>5.745</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.312</v>
+        <v>-0.2949</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.847</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.312</v>
+        <v>-0.2949</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.847</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.51</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1421</v>
+        <v>1.1502</v>
       </c>
       <c r="J42" t="n">
-        <v>25.1262</v>
+        <v>25.3044</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.36</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8607</v>
+        <v>0.8426</v>
       </c>
       <c r="J43" t="n">
-        <v>18.9354</v>
+        <v>18.5372</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.35</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8413</v>
+        <v>0.822</v>
       </c>
       <c r="J44" t="n">
-        <v>18.5086</v>
+        <v>18.084</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>1.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.401</v>
+        <v>0.3683</v>
       </c>
       <c r="J45" t="n">
-        <v>8.821999999999999</v>
+        <v>8.102600000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.93</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3071</v>
+        <v>-0.2688</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.7562</v>
+        <v>-5.9136</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3164</v>
+        <v>0.2942</v>
       </c>
       <c r="J47" t="n">
-        <v>6.9608</v>
+        <v>6.4724</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.59</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4087</v>
+        <v>-0.3992</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.991400000000001</v>
+        <v>-8.782400000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4351</v>
+        <v>-0.4272</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.5722</v>
+        <v>-9.398400000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.53</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4615</v>
+        <v>-0.4558</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.153</v>
+        <v>-10.0276</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.52</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4703</v>
+        <v>-0.4654</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.3466</v>
+        <v>-10.2388</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3779</v>
+        <v>0.3282</v>
       </c>
       <c r="J52" t="n">
-        <v>9.4475</v>
+        <v>8.205</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>0.96</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0562</v>
+        <v>-0.0455</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.405</v>
+        <v>-1.1375</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1442</v>
+        <v>-0.1282</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.605</v>
+        <v>-3.205</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.57</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4473</v>
+        <v>-0.4404</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.1825</v>
+        <v>-11.01</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.57</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4473</v>
+        <v>-0.4404</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.1825</v>
+        <v>-11.01</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8956</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>22.39</v>
+        <v>22.0125</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>1.31</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6774</v>
       </c>
       <c r="J58" t="n">
-        <v>17.3</v>
+        <v>16.935</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4881</v>
+        <v>0.4688</v>
       </c>
       <c r="J59" t="n">
-        <v>12.2025</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.96</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1985</v>
+        <v>-0.1639</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.9625</v>
+        <v>-4.0975</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.91</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3464</v>
+        <v>-0.3049</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.66</v>
+        <v>-7.6225</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.12</v>
       </c>
       <c r="I62" t="n">
-        <v>0.303</v>
+        <v>0.2522</v>
       </c>
       <c r="J62" t="n">
-        <v>12.12</v>
+        <v>10.088</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0509</v>
+        <v>0.0342</v>
       </c>
       <c r="J63" t="n">
-        <v>2.036</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1752</v>
+        <v>-0.1553</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.008</v>
+        <v>-6.212</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.86</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1859</v>
+        <v>-0.1658</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.436</v>
+        <v>-6.632</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1859</v>
+        <v>-0.1658</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.436</v>
+        <v>-6.632</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.09</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3151</v>
+        <v>0.2741</v>
       </c>
       <c r="J67" t="n">
-        <v>12.604</v>
+        <v>10.964</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.06</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2304</v>
+        <v>0.1937</v>
       </c>
       <c r="J68" t="n">
-        <v>9.215999999999999</v>
+        <v>7.748</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.03</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1354</v>
+        <v>0.1076</v>
       </c>
       <c r="J69" t="n">
-        <v>5.416</v>
+        <v>4.304</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1354</v>
+        <v>-0.1076</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.416</v>
+        <v>-4.304</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4689</v>
+        <v>-0.4262</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.756</v>
+        <v>-17.048</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.15</v>
       </c>
       <c r="I72" t="n">
-        <v>0.368</v>
+        <v>0.3142</v>
       </c>
       <c r="J72" t="n">
-        <v>10.304</v>
+        <v>8.797599999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3493</v>
+        <v>0.2964</v>
       </c>
       <c r="J73" t="n">
-        <v>9.7804</v>
+        <v>8.299200000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>0.86</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1831</v>
+        <v>-0.1635</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.1268</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>0.73</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3115</v>
+        <v>-0.294</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.722</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3578</v>
+        <v>-0.3432</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.0184</v>
+        <v>-9.6096</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.35</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7912</v>
+        <v>0.7771</v>
       </c>
       <c r="J77" t="n">
-        <v>22.1536</v>
+        <v>21.7588</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.059</v>
+        <v>0.0428</v>
       </c>
       <c r="J78" t="n">
-        <v>1.652</v>
+        <v>1.1984</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2301</v>
+        <v>-0.1934</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.4428</v>
+        <v>-5.4152</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.92</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2873</v>
+        <v>-0.2474</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.0444</v>
+        <v>-6.9272</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.77</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6553</v>
+        <v>-0.6193</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.3484</v>
+        <v>-17.3404</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.45</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6857</v>
       </c>
       <c r="J82" t="n">
-        <v>21.579</v>
+        <v>20.571</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.18</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3945</v>
+        <v>0.3385</v>
       </c>
       <c r="J83" t="n">
-        <v>11.835</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1133</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.399</v>
+        <v>-2.856</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1929</v>
+        <v>-0.1722</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.787</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3587</v>
+        <v>-0.345</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.761</v>
+        <v>-10.35</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.15</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4783</v>
+        <v>0.4509</v>
       </c>
       <c r="J87" t="n">
-        <v>14.349</v>
+        <v>13.527</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.03</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1514</v>
+        <v>0.1204</v>
       </c>
       <c r="J88" t="n">
-        <v>4.542</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3795</v>
+        <v>-0.3389</v>
       </c>
       <c r="J89" t="n">
-        <v>-11.385</v>
+        <v>-10.167</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5252</v>
+        <v>-0.4844</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.756</v>
+        <v>-14.532</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.76</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6623</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.869</v>
+        <v>-18.795</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.75</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4563</v>
+        <v>1.4916</v>
       </c>
       <c r="J92" t="n">
-        <v>39.3201</v>
+        <v>40.2732</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>1.15</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4407</v>
+        <v>0.4029</v>
       </c>
       <c r="J93" t="n">
-        <v>11.8989</v>
+        <v>10.8783</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.294</v>
+        <v>0.2599</v>
       </c>
       <c r="J94" t="n">
-        <v>7.938</v>
+        <v>7.0173</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4208</v>
+        <v>-0.3785</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.3616</v>
+        <v>-10.2195</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5911</v>
+        <v>-0.5538</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.9597</v>
+        <v>-14.9526</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.15</v>
       </c>
       <c r="I97" t="n">
-        <v>0.394</v>
+        <v>0.3433</v>
       </c>
       <c r="J97" t="n">
-        <v>10.638</v>
+        <v>9.2691</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0848</v>
+        <v>-0.0718</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.2896</v>
+        <v>-1.9386</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>0.89</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1451</v>
+        <v>-0.1289</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.9177</v>
+        <v>-3.4803</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>0.66</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3679</v>
+        <v>-0.3539</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.933299999999999</v>
+        <v>-9.555300000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.53</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4831</v>
+        <v>-0.4804</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.0437</v>
+        <v>-12.9708</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4612</v>
+        <v>0.4653</v>
       </c>
       <c r="J102" t="n">
-        <v>12.9136</v>
+        <v>13.0284</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3209</v>
+        <v>0.3104</v>
       </c>
       <c r="J103" t="n">
-        <v>8.985200000000001</v>
+        <v>8.6912</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>1.06</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1299</v>
+        <v>0.1144</v>
       </c>
       <c r="J104" t="n">
-        <v>3.6372</v>
+        <v>3.2032</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2453</v>
+        <v>-0.2253</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.8684</v>
+        <v>-6.3084</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.8</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2553</v>
+        <v>-0.2356</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.1484</v>
+        <v>-6.5968</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.32</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4779</v>
+        <v>0.4127</v>
       </c>
       <c r="J107" t="n">
-        <v>13.3812</v>
+        <v>11.5556</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2919</v>
+        <v>0.237</v>
       </c>
       <c r="J108" t="n">
-        <v>8.1732</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.14</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2514</v>
+        <v>0.2005</v>
       </c>
       <c r="J109" t="n">
-        <v>7.0392</v>
+        <v>5.614</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>0.6</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4333</v>
+        <v>-0.4261</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.1324</v>
+        <v>-11.9308</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4854</v>
+        <v>-0.4845</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.5912</v>
+        <v>-13.566</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.84</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5379</v>
+        <v>1.5759</v>
       </c>
       <c r="J112" t="n">
-        <v>33.8338</v>
+        <v>34.6698</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.25</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6451</v>
+        <v>0.6155</v>
       </c>
       <c r="J113" t="n">
-        <v>14.1922</v>
+        <v>13.541</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5407</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>11.8954</v>
+        <v>11.1892</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4035</v>
+        <v>0.3704</v>
       </c>
       <c r="J115" t="n">
-        <v>8.877000000000001</v>
+        <v>8.1488</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6776</v>
+        <v>-0.6483</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.9072</v>
+        <v>-14.2626</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.41</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.837</v>
       </c>
       <c r="J117" t="n">
-        <v>18.9288</v>
+        <v>18.414</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1514</v>
+        <v>-0.1356</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.3308</v>
+        <v>-2.9832</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.71</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3177</v>
+        <v>-0.3013</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.9894</v>
+        <v>-6.6286</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.64</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3815</v>
+        <v>-0.3685</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.393000000000001</v>
+        <v>-8.106999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.33</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6496</v>
+        <v>-0.6728</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.2912</v>
+        <v>-14.8016</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6571</v>
+        <v>0.6213</v>
       </c>
       <c r="J122" t="n">
-        <v>19.713</v>
+        <v>18.639</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4454</v>
+        <v>0.4025</v>
       </c>
       <c r="J123" t="n">
-        <v>13.362</v>
+        <v>12.075</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3161</v>
+        <v>0.2749</v>
       </c>
       <c r="J124" t="n">
-        <v>9.483000000000001</v>
+        <v>8.247</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>0.78</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6323</v>
+        <v>-0.5951</v>
       </c>
       <c r="J125" t="n">
-        <v>-18.969</v>
+        <v>-17.853</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7216</v>
+        <v>-0.6899</v>
       </c>
       <c r="J126" t="n">
-        <v>-21.648</v>
+        <v>-20.697</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.62</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0643</v>
+        <v>1.0531</v>
       </c>
       <c r="J127" t="n">
-        <v>31.929</v>
+        <v>31.593</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.14</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3364</v>
+        <v>0.2833</v>
       </c>
       <c r="J128" t="n">
-        <v>10.092</v>
+        <v>8.499000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2974</v>
+        <v>-0.2792</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.922000000000001</v>
+        <v>-8.375999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.72</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3257</v>
+        <v>-0.3091</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.771000000000001</v>
+        <v>-9.273</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4515</v>
+        <v>-0.4464</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.545</v>
+        <v>-13.392</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8821</v>
+        <v>0.8627</v>
       </c>
       <c r="J132" t="n">
-        <v>21.1704</v>
+        <v>20.7048</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.29</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7408</v>
+        <v>0.7114</v>
       </c>
       <c r="J133" t="n">
-        <v>17.7792</v>
+        <v>17.0736</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6784</v>
+        <v>0.646</v>
       </c>
       <c r="J134" t="n">
-        <v>16.2816</v>
+        <v>15.504</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0747</v>
+        <v>0.0582</v>
       </c>
       <c r="J135" t="n">
-        <v>1.7928</v>
+        <v>1.3968</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.87</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4506</v>
+        <v>-0.4091</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.8144</v>
+        <v>-9.8184</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5473</v>
+        <v>0.4987</v>
       </c>
       <c r="J137" t="n">
-        <v>13.1352</v>
+        <v>11.9688</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1651</v>
+        <v>-0.1487</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.9624</v>
+        <v>-3.5688</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1863</v>
+        <v>-0.1693</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.4712</v>
+        <v>-4.0632</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.62</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4019</v>
+        <v>-0.3905</v>
       </c>
       <c r="J140" t="n">
-        <v>-9.6456</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.51</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4986</v>
+        <v>-0.4977</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.9664</v>
+        <v>-11.9448</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.08</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2481</v>
+        <v>0.2039</v>
       </c>
       <c r="J142" t="n">
-        <v>5.9544</v>
+        <v>4.8936</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.97</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0448</v>
+        <v>-0.0356</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.0752</v>
+        <v>-0.8544</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.78</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2576</v>
+        <v>-0.2388</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.1824</v>
+        <v>-5.7312</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2957</v>
+        <v>-0.2778</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.0968</v>
+        <v>-6.6672</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.68</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3514</v>
+        <v>-0.3362</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.4336</v>
+        <v>-8.0688</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.58</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2343</v>
+        <v>1.253</v>
       </c>
       <c r="J147" t="n">
-        <v>29.6232</v>
+        <v>30.072</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.37</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9129</v>
+        <v>0.8961</v>
       </c>
       <c r="J148" t="n">
-        <v>21.9096</v>
+        <v>21.5064</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.11</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3475</v>
+        <v>0.3106</v>
       </c>
       <c r="J149" t="n">
-        <v>8.34</v>
+        <v>7.4544</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>0.93</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2825</v>
+        <v>-0.2423</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.78</v>
+        <v>-5.8152</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.018</v>
+        <v>-1.0199</v>
       </c>
       <c r="J151" t="n">
-        <v>-24.432</v>
+        <v>-24.4776</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.54</v>
       </c>
       <c r="I152" t="n">
-        <v>0.955</v>
+        <v>0.9173</v>
       </c>
       <c r="J152" t="n">
-        <v>26.74</v>
+        <v>25.6844</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.36</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6912</v>
+        <v>0.6347</v>
       </c>
       <c r="J153" t="n">
-        <v>19.3536</v>
+        <v>17.7716</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.8</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2522</v>
+        <v>-0.2323</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.0616</v>
+        <v>-6.5044</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.66</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3839</v>
+        <v>-0.3721</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.7492</v>
+        <v>-10.4188</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.63</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4106</v>
+        <v>-0.4015</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.4968</v>
+        <v>-11.242</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.21</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>17.7408</v>
+        <v>16.7524</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.08</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3047</v>
+        <v>0.2633</v>
       </c>
       <c r="J158" t="n">
-        <v>8.531599999999999</v>
+        <v>7.3724</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>0.91</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3032</v>
+        <v>-0.2649</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.489599999999999</v>
+        <v>-7.4172</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6192</v>
+        <v>-0.5813</v>
       </c>
       <c r="J160" t="n">
-        <v>-17.3376</v>
+        <v>-16.2764</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>0.7</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7953</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.2684</v>
+        <v>-21.5208</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.495</v>
+        <v>0.512</v>
       </c>
       <c r="J162" t="n">
-        <v>13.86</v>
+        <v>14.336</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>0.95</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0743</v>
+        <v>-0.0622</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.0804</v>
+        <v>-1.7416</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>0.84</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1991</v>
+        <v>-0.1806</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.5748</v>
+        <v>-5.0568</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3244</v>
+        <v>-0.3077</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.0832</v>
+        <v>-8.615600000000001</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>0.49</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5222</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.5516</v>
+        <v>-14.6216</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.52</v>
       </c>
       <c r="I167" t="n">
-        <v>0.667</v>
+        <v>0.5966</v>
       </c>
       <c r="J167" t="n">
-        <v>18.676</v>
+        <v>16.7048</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>1.25</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3696</v>
+        <v>0.3083</v>
       </c>
       <c r="J168" t="n">
-        <v>10.3488</v>
+        <v>8.632400000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.96</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0794</v>
+        <v>-0.0639</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.2232</v>
+        <v>-1.7892</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.92</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.131</v>
+        <v>-0.1118</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.668</v>
+        <v>-3.1304</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.79</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2699</v>
+        <v>-0.2511</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.5572</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1024</v>
+        <v>1.1151</v>
       </c>
       <c r="J172" t="n">
-        <v>25.3552</v>
+        <v>25.6473</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.48</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1024</v>
+        <v>1.1151</v>
       </c>
       <c r="J173" t="n">
-        <v>25.3552</v>
+        <v>25.6473</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.95</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2178</v>
+        <v>-0.1809</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.0094</v>
+        <v>-4.1607</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.569</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.9472</v>
+        <v>-13.087</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6968</v>
+        <v>-0.6651</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.0264</v>
+        <v>-15.2973</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5885</v>
+        <v>0.5387</v>
       </c>
       <c r="J177" t="n">
-        <v>13.5355</v>
+        <v>12.3901</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>0.95</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0722</v>
+        <v>-0.0602</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.6606</v>
+        <v>-1.3846</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>0.82</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2178</v>
+        <v>-0.1993</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.0094</v>
+        <v>-4.5839</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>0.7</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3319</v>
+        <v>-0.3157</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.6337</v>
+        <v>-7.2611</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.47</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5353</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.3119</v>
+        <v>-12.4154</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.9</v>
       </c>
       <c r="I182" t="n">
-        <v>1.5749</v>
+        <v>1.6125</v>
       </c>
       <c r="J182" t="n">
-        <v>34.6478</v>
+        <v>35.475</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.47</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0315</v>
+        <v>1.0387</v>
       </c>
       <c r="J183" t="n">
-        <v>22.693</v>
+        <v>22.8514</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.31</v>
       </c>
       <c r="I184" t="n">
-        <v>0.7492</v>
+        <v>0.7309</v>
       </c>
       <c r="J184" t="n">
-        <v>16.4824</v>
+        <v>16.0798</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>1.31</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7492</v>
+        <v>0.7309</v>
       </c>
       <c r="J185" t="n">
-        <v>16.4824</v>
+        <v>16.0798</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3267</v>
+        <v>-0.292</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.1874</v>
+        <v>-6.424</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>0.97</v>
       </c>
       <c r="I187" t="n">
-        <v>0.015</v>
+        <v>0.0474</v>
       </c>
       <c r="J187" t="n">
-        <v>0.33</v>
+        <v>1.0428</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>0.71</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2982</v>
+        <v>-0.2865</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.5604</v>
+        <v>-6.303</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>0.52</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.466</v>
+        <v>-0.461</v>
       </c>
       <c r="J189" t="n">
-        <v>-10.252</v>
+        <v>-10.142</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5012</v>
+        <v>-0.4995</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.0264</v>
+        <v>-10.989</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.44</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5365</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.803</v>
+        <v>-11.8536</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.46</v>
       </c>
       <c r="I192" t="n">
-        <v>1.086</v>
+        <v>1.0986</v>
       </c>
       <c r="J192" t="n">
-        <v>30.408</v>
+        <v>30.7608</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.21</v>
       </c>
       <c r="I193" t="n">
-        <v>0.595</v>
+        <v>0.5562</v>
       </c>
       <c r="J193" t="n">
-        <v>16.66</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.17</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5031</v>
+        <v>0.4618</v>
       </c>
       <c r="J194" t="n">
-        <v>14.0868</v>
+        <v>12.9304</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>0.74</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.7329</v>
+        <v>-0.703</v>
       </c>
       <c r="J195" t="n">
-        <v>-20.5212</v>
+        <v>-19.684</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>0.68</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8618</v>
+        <v>-0.8435</v>
       </c>
       <c r="J196" t="n">
-        <v>-24.1304</v>
+        <v>-23.618</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.401</v>
+        <v>0.3457</v>
       </c>
       <c r="J197" t="n">
-        <v>11.228</v>
+        <v>9.679600000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0545</v>
+        <v>0.037</v>
       </c>
       <c r="J198" t="n">
-        <v>1.526</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1518</v>
+        <v>-0.1331</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.2504</v>
+        <v>-3.7268</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2353</v>
+        <v>-0.2153</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.5884</v>
+        <v>-6.0284</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.74</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3032</v>
+        <v>-0.2853</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.489599999999999</v>
+        <v>-7.9884</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7839</v>
+        <v>0.7569</v>
       </c>
       <c r="J202" t="n">
-        <v>22.7331</v>
+        <v>21.9501</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>1.1</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3396</v>
+        <v>0.298</v>
       </c>
       <c r="J203" t="n">
-        <v>9.8484</v>
+        <v>8.641999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.98</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1009</v>
+        <v>-0.0774</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.9261</v>
+        <v>-2.2446</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.84</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4952</v>
+        <v>-0.453</v>
       </c>
       <c r="J205" t="n">
-        <v>-14.3608</v>
+        <v>-13.137</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.84</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4952</v>
+        <v>-0.453</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.3608</v>
+        <v>-13.137</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3654</v>
+        <v>0.3107</v>
       </c>
       <c r="J207" t="n">
-        <v>10.5966</v>
+        <v>9.010300000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2536</v>
+        <v>0.2069</v>
       </c>
       <c r="J208" t="n">
-        <v>7.3544</v>
+        <v>6.0001</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0721</v>
+        <v>-0.0579</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.0909</v>
+        <v>-1.6791</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0985</v>
+        <v>-0.0818</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.8565</v>
+        <v>-2.3722</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2419</v>
+        <v>-0.2217</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.0151</v>
+        <v>-6.4293</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>1.11</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3648</v>
+        <v>0.3227</v>
       </c>
       <c r="J212" t="n">
-        <v>9.849600000000001</v>
+        <v>8.712899999999999</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>1.02</v>
       </c>
       <c r="I213" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0755</v>
       </c>
       <c r="J213" t="n">
-        <v>2.6352</v>
+        <v>2.0385</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>1.01</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0574</v>
+        <v>0.0422</v>
       </c>
       <c r="J214" t="n">
-        <v>1.5498</v>
+        <v>1.1394</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1377</v>
+        <v>-0.1091</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.7179</v>
+        <v>-2.9457</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.1712</v>
+        <v>-0.139</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.6224</v>
+        <v>-3.753</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.13</v>
       </c>
       <c r="I217" t="n">
-        <v>0.322</v>
+        <v>0.27</v>
       </c>
       <c r="J217" t="n">
-        <v>8.694000000000001</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.02</v>
       </c>
       <c r="I218" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="J218" t="n">
-        <v>2.2032</v>
+        <v>1.566</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>0.95</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0684</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.2302</v>
+        <v>-1.8468</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1073</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.8971</v>
+        <v>-2.4543</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3517</v>
+        <v>-0.3368</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.495900000000001</v>
+        <v>-9.0936</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.39</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9566</v>
+        <v>0.946</v>
       </c>
       <c r="J222" t="n">
-        <v>21.0452</v>
+        <v>20.812</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.38</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9377</v>
+        <v>0.9242</v>
       </c>
       <c r="J223" t="n">
-        <v>20.6294</v>
+        <v>20.3324</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7339</v>
+        <v>0.7028</v>
       </c>
       <c r="J224" t="n">
-        <v>16.1458</v>
+        <v>15.4616</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.676</v>
+        <v>-0.643</v>
       </c>
       <c r="J225" t="n">
-        <v>-14.872</v>
+        <v>-14.146</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8498</v>
+        <v>-0.8316</v>
       </c>
       <c r="J226" t="n">
-        <v>-18.6956</v>
+        <v>-18.2952</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.23</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5309</v>
+        <v>0.4784</v>
       </c>
       <c r="J227" t="n">
-        <v>11.6798</v>
+        <v>10.5248</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1791</v>
+        <v>-0.1611</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.9402</v>
+        <v>-3.5442</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2288</v>
+        <v>-0.2098</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.0336</v>
+        <v>-4.6156</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2288</v>
+        <v>-0.2098</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.0336</v>
+        <v>-4.6156</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.459</v>
+        <v>-0.4536</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.098</v>
+        <v>-9.979200000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>2.01</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7171</v>
+        <v>1.7698</v>
       </c>
       <c r="J232" t="n">
-        <v>36.0591</v>
+        <v>37.1658</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.44</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9911</v>
+        <v>0.9907</v>
       </c>
       <c r="J233" t="n">
-        <v>20.8131</v>
+        <v>20.8047</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.34</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8115</v>
+        <v>0.7946</v>
       </c>
       <c r="J234" t="n">
-        <v>17.0415</v>
+        <v>16.6866</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>1.07</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2053</v>
+        <v>0.1758</v>
       </c>
       <c r="J235" t="n">
-        <v>4.3113</v>
+        <v>3.6918</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.85</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5298</v>
+        <v>-0.4953</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.1258</v>
+        <v>-10.4013</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>0.86</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1462</v>
+        <v>-0.1287</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.0702</v>
+        <v>-2.7027</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>0.78</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2335</v>
+        <v>-0.2191</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.9035</v>
+        <v>-4.6011</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.66</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.348</v>
+        <v>-0.3368</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.308</v>
+        <v>-7.0728</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.5</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4873</v>
+        <v>-0.4841</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.2333</v>
+        <v>-10.1661</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5313</v>
+        <v>-0.5331</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.1573</v>
+        <v>-11.1951</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.29</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7696</v>
+        <v>0.7407</v>
       </c>
       <c r="J242" t="n">
-        <v>26.1664</v>
+        <v>25.1838</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.27</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7269</v>
+        <v>0.695</v>
       </c>
       <c r="J243" t="n">
-        <v>24.7146</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0931</v>
+        <v>0.0732</v>
       </c>
       <c r="J244" t="n">
-        <v>3.1654</v>
+        <v>2.4888</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>0.86</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4549</v>
+        <v>-0.4121</v>
       </c>
       <c r="J245" t="n">
-        <v>-15.4666</v>
+        <v>-14.0114</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5515</v>
+        <v>-0.5111</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.751</v>
+        <v>-17.3774</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.22</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5007</v>
+        <v>0.4455</v>
       </c>
       <c r="J247" t="n">
-        <v>17.0238</v>
+        <v>15.147</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2154</v>
+        <v>0.1729</v>
       </c>
       <c r="J248" t="n">
-        <v>7.3236</v>
+        <v>5.8786</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.99</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0158</v>
+        <v>-0.0112</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.5372</v>
+        <v>-0.3808</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.67</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3645</v>
+        <v>-0.3503</v>
       </c>
       <c r="J250" t="n">
-        <v>-12.393</v>
+        <v>-11.9102</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.49</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5225</v>
+        <v>-0.5259</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.765</v>
+        <v>-17.8806</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.5</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1385</v>
+        <v>1.1539</v>
       </c>
       <c r="J252" t="n">
-        <v>31.878</v>
+        <v>32.3092</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1.05</v>
       </c>
       <c r="I253" t="n">
-        <v>0.191</v>
+        <v>0.1605</v>
       </c>
       <c r="J253" t="n">
-        <v>5.348</v>
+        <v>4.494</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1474</v>
+        <v>-0.1168</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.1272</v>
+        <v>-3.2704</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.91</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3286</v>
+        <v>-0.2865</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.200799999999999</v>
+        <v>-8.022</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3286</v>
+        <v>-0.2865</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.200799999999999</v>
+        <v>-8.022</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1</v>
       </c>
       <c r="I257" t="n">
-        <v>0.0288</v>
+        <v>0.023</v>
       </c>
       <c r="J257" t="n">
-        <v>0.8064</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>0.95</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0725</v>
+        <v>-0.0605</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.03</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>0.8</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2375</v>
+        <v>-0.2188</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.65</v>
+        <v>-6.1264</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.75</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2854</v>
+        <v>-0.2673</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.9912</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.71</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3229</v>
+        <v>-0.3062</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.0412</v>
+        <v>-8.573600000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.89</v>
       </c>
       <c r="I262" t="n">
-        <v>1.592</v>
+        <v>1.6341</v>
       </c>
       <c r="J262" t="n">
-        <v>35.024</v>
+        <v>35.9502</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.63</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2629</v>
+        <v>1.2804</v>
       </c>
       <c r="J263" t="n">
-        <v>27.7838</v>
+        <v>28.1688</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.18</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4924</v>
+        <v>0.4606</v>
       </c>
       <c r="J264" t="n">
-        <v>10.8328</v>
+        <v>10.1332</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2797</v>
+        <v>-0.2428</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.1534</v>
+        <v>-5.3416</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.71</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.8193</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.3524</v>
+        <v>-18.0246</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0556</v>
+        <v>-0.0428</v>
       </c>
       <c r="J267" t="n">
-        <v>-1.2232</v>
+        <v>-0.9416</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1661</v>
+        <v>-0.1505</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.6542</v>
+        <v>-3.311</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2766</v>
+        <v>-0.261</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.0852</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4291</v>
+        <v>-0.4201</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.440200000000001</v>
+        <v>-9.2422</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4291</v>
+        <v>-0.4201</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.440200000000001</v>
+        <v>-9.2422</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>2.03</v>
       </c>
       <c r="I272" t="n">
-        <v>1.7496</v>
+        <v>1.8072</v>
       </c>
       <c r="J272" t="n">
-        <v>34.992</v>
+        <v>36.144</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.75</v>
       </c>
       <c r="I273" t="n">
-        <v>1.407</v>
+        <v>1.4326</v>
       </c>
       <c r="J273" t="n">
-        <v>28.14</v>
+        <v>28.652</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.07</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2101</v>
+        <v>0.1808</v>
       </c>
       <c r="J274" t="n">
-        <v>4.202</v>
+        <v>3.616</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.476</v>
+        <v>-0.439</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.52</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.84</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5494</v>
+        <v>-0.5149</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.988</v>
+        <v>-10.298</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1097</v>
+        <v>0.0934</v>
       </c>
       <c r="J277" t="n">
-        <v>2.194</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.96</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0398</v>
+        <v>-0.0277</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.796</v>
+        <v>-0.554</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.6</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4106</v>
+        <v>-0.4001</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.212</v>
+        <v>-8.002000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.446</v>
+        <v>-0.4386</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.92</v>
+        <v>-8.772</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.446</v>
+        <v>-0.4386</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.92</v>
+        <v>-8.772</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.48</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0791</v>
+        <v>1.0884</v>
       </c>
       <c r="J282" t="n">
-        <v>28.0566</v>
+        <v>28.2984</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>1.36</v>
       </c>
       <c r="I283" t="n">
-        <v>0.8752</v>
+        <v>0.8559</v>
       </c>
       <c r="J283" t="n">
-        <v>22.7552</v>
+        <v>22.2534</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>1.3</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7553</v>
+        <v>0.7278</v>
       </c>
       <c r="J284" t="n">
-        <v>19.6378</v>
+        <v>18.9228</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>1.03</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1062</v>
+        <v>0.0857</v>
       </c>
       <c r="J285" t="n">
-        <v>2.7612</v>
+        <v>2.2282</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.77</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6912</v>
+        <v>-0.6614</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.9712</v>
+        <v>-17.1964</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>0.0452</v>
+        <v>0.0398</v>
       </c>
       <c r="J287" t="n">
-        <v>1.1752</v>
+        <v>1.0348</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>0.95</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0641</v>
+        <v>-0.0521</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.6666</v>
+        <v>-1.3546</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>0.82</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.214</v>
+        <v>-0.1973</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.564</v>
+        <v>-5.1298</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>0.79</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2429</v>
+        <v>-0.2258</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.3154</v>
+        <v>-5.8708</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.38</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.607</v>
+        <v>-0.6223</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.782</v>
+        <v>-16.1798</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.12</v>
       </c>
       <c r="I292" t="n">
-        <v>0.2876</v>
+        <v>0.2383</v>
       </c>
       <c r="J292" t="n">
-        <v>8.628</v>
+        <v>7.149</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2687</v>
+        <v>0.221</v>
       </c>
       <c r="J293" t="n">
-        <v>8.061</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>1.02</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0717</v>
+        <v>0.0517</v>
       </c>
       <c r="J294" t="n">
-        <v>2.151</v>
+        <v>1.551</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1005</v>
+        <v>-0.0833</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.015</v>
+        <v>-2.499</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.9</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1485</v>
+        <v>-0.1287</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.455</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.15</v>
       </c>
       <c r="I297" t="n">
-        <v>0.476</v>
+        <v>0.4334</v>
       </c>
       <c r="J297" t="n">
-        <v>14.28</v>
+        <v>13.002</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.11</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3746</v>
+        <v>0.3317</v>
       </c>
       <c r="J298" t="n">
-        <v>11.238</v>
+        <v>9.951000000000001</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.04</v>
       </c>
       <c r="I299" t="n">
-        <v>0.1736</v>
+        <v>0.1408</v>
       </c>
       <c r="J299" t="n">
-        <v>5.208</v>
+        <v>4.224</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>0.88</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3891</v>
+        <v>-0.3468</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.673</v>
+        <v>-10.404</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>0.7</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8041</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="J301" t="n">
-        <v>-24.123</v>
+        <v>-23.361</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>0.99</v>
       </c>
       <c r="I302" t="n">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="J302" t="n">
-        <v>-0</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1034</v>
+        <v>-0.0893</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.1714</v>
+        <v>-1.8753</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>0.83</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.204</v>
+        <v>-0.1874</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.284</v>
+        <v>-3.9354</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.68</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3445</v>
+        <v>-0.3294</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.2345</v>
+        <v>-6.9174</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4869</v>
+        <v>-0.4843</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.2249</v>
+        <v>-10.1703</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.34</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8343</v>
+        <v>0.8121</v>
       </c>
       <c r="J307" t="n">
-        <v>17.5203</v>
+        <v>17.0541</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.26</v>
       </c>
       <c r="I308" t="n">
-        <v>0.6721</v>
+        <v>0.6409</v>
       </c>
       <c r="J308" t="n">
-        <v>14.1141</v>
+        <v>13.4589</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.22</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5545</v>
       </c>
       <c r="J309" t="n">
-        <v>12.3522</v>
+        <v>11.6445</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.17</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4803</v>
+        <v>0.4454</v>
       </c>
       <c r="J310" t="n">
-        <v>10.0863</v>
+        <v>9.353400000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.98</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1338</v>
+        <v>-0.1066</v>
       </c>
       <c r="J311" t="n">
-        <v>-2.8098</v>
+        <v>-2.2386</v>
       </c>
     </row>
   </sheetData>
